--- a/server/excel/release/cyclic-shop.xlsx
+++ b/server/excel/release/cyclic-shop.xlsx
@@ -94,7 +94,7 @@
     <t xml:space="preserve">Đồ cất giữ thức tỉnh gói quà</t>
   </si>
   <si>
-    <t xml:space="preserve">Trợ lực thú linh Nguyên bảo</t>
+    <t xml:space="preserve">Trợ lực thú linh Kim cương</t>
   </si>
   <si>
     <t xml:space="preserve">Trợ lực tướng vượt phục</t>

--- a/server/excel/release/cyclic-shop.xlsx
+++ b/server/excel/release/cyclic-shop.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="循环商城基础" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="循环商城商品" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="自然日期商城基础" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="自然日期商城商品" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="自然日兑换商城基础" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="自然日兑换商城商品" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="自然日研磨商城基础" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Sheet1" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="自然日研磨商城商品" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="循环商城基础" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="循环商城商品" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="自然日期商城基础" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="自然日期商城商品" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="自然日兑换商城基础" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="自然日兑换商城商品" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="自然日研磨商城基础" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="自然日研磨商城商品" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="817" uniqueCount="817">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="819" uniqueCount="819">
   <si>
     <t xml:space="preserve">ID</t>
   </si>
@@ -145,37 +145,37 @@
     <t xml:space="preserve">0:1:300#3:500019:2#3:100018:50#0:0:2000000</t>
   </si>
   <si>
-    <t xml:space="preserve">元宝*300，遗物自选*2，信仰之力*50，金币*200w</t>
+    <t xml:space="preserve">Kim cương*300, Di vật tự do gói quà*2, Tín ngưỡng chi lực*50, Beri*2M</t>
   </si>
   <si>
     <t xml:space="preserve">0:1:680#3:500019:4#3:100018:100#0:0:5000000</t>
   </si>
   <si>
-    <t xml:space="preserve">元宝*680，遗物自选*4，信仰之力*100，金币*500w</t>
+    <t xml:space="preserve">Kim cương*680, Di vật tự do gói quà*4, Tín ngưỡng chi lực*100, Beri*5M</t>
   </si>
   <si>
     <t xml:space="preserve">0:1:1280#3:500019:6#3:100018:150#0:0:8000000</t>
   </si>
   <si>
-    <t xml:space="preserve">元宝*1280，遗物自选*6，信仰之力*150，金币*800w</t>
+    <t xml:space="preserve">Kim cương*1,28K, Di vật tự do gói quà*6, Tín ngưỡng chi lực*150, Beri*8M</t>
   </si>
   <si>
     <t xml:space="preserve">0:1:1980#3:500019:8#3:100018:200#0:0:10000000</t>
   </si>
   <si>
-    <t xml:space="preserve">元宝*1980，遗物自选*8，信仰之力*200，金币*1000w</t>
+    <t xml:space="preserve">Kim cương*1,98K, Di vật tự do gói quà*8, Tín ngưỡng chi lực*200, Beri*10M</t>
   </si>
   <si>
     <t xml:space="preserve">0:1:3280#3:500019:11#3:100018:300#0:0:20000000</t>
   </si>
   <si>
-    <t xml:space="preserve">元宝*3280，遗物自选*11，信仰之力*300，金币*2000w</t>
+    <t xml:space="preserve">Kim cương*3,28K, Di vật tự do gói quà*11, Tín ngưỡng chi lực*300, Beri*20M</t>
   </si>
   <si>
     <t xml:space="preserve">0:1:6480#3:500019:18#3:100018:500#0:0:40000000</t>
   </si>
   <si>
-    <t xml:space="preserve">元宝*6480，遗物自选*18，信仰之力*500，金币*4000w</t>
+    <t xml:space="preserve">Kim cương*6,48K, Di vật tự do gói quà*18, Tín ngưỡng chi lực*500, Beri*40M</t>
   </si>
   <si>
     <t xml:space="preserve">0:1:120#3:100059:20#0:0:2000000</t>
@@ -355,1885 +355,1891 @@
     <t xml:space="preserve">3:100252:10</t>
   </si>
   <si>
+    <t xml:space="preserve">Hoa hồng*10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3:100255:1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sách kỹ năng Nữ Tặc*1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3:100253:10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kho báu*10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0:1:450#3:300045:1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kim cương*450, Ngọc trợ lực gói quà*1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0:1:980#3:100252:100#3:590008:1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kim cương*980, Hoa hồng*100, Hảo vận lì xì*1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0:1:1980#3:100252:100#3:100098:1000#3:590008:2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kim cương*1,98K, Hoa hồng*100, Bản đồ kho báu*1K, Hảo vận lì xì*2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4:606002:50</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mảnh 5 Tinh ngẫu nhiên mảnh*50</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3:100023:5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Truy nã cướp biển*5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0:1:450#4:606002:50</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kim cương*450, Mảnh 5 Tinh ngẫu nhiên mảnh*50</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0:1:980#3:100044:15#3:590012:4#3:590008:1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kim cương*980, Tinh anh điểm tướng khoán*15, Cao cấp diễn võ gói quà*4, Hảo vận lì xì*1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0:1:1980#3:100044:30#3:590012:10#3:590008:2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kim cương*1,98K, Tinh anh điểm tướng khoán*30, Cao cấp diễn võ gói quà*10, Hảo vận lì xì*2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3:100004:1500</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Đá vàng*1,5K</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3:100006:4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chìa khóa tầm bảo cao cấp*4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0:1:450#3:100006:10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kim cương*450, Chìa khóa tầm bảo cao cấp*10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0:1:980#3:100004:8000#3:100006:10#3:590008:1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kim cương*980, Đá vàng*8K, Chìa khóa tầm bảo cao cấp*10, Hảo vận lì xì*1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0:1:1980#3:100004:16000#3:100006:30#3:590008:2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kim cương*1,98K, Đá vàng*16K, Chìa khóa tầm bảo cao cấp*30, Hảo vận lì xì*2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">开服天数</t>
+  </si>
+  <si>
+    <t xml:space="preserve">活动期间达标开启</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vật tư thương thành</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2020-08-21 00:00:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2020-08-27 23:59:59</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2020-10-09 00:00:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2020-10-15 23:59:59</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2020-11-20 00:00:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2020-11-26 23:59:59</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2020-12-25 00:00:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2020-12-31 23:59:59</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2021-01-29 00:00:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2021-02-04 23:59:59</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2021-03-12 00:00:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2021-03-18 23:59:59</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2021-04-09 09:00:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2021-04-15 23:59:59</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2021-05-07 09:00:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2021-05-13 23:59:59</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2021-06-04 09:00:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2021-06-10 23:59:59</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2021-07-02 09:00:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2021-07-08 23:59:59</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2021-07-30 09:00:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2021-08-05 23:59:59</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2021-09-10 09:00:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2021-09-16 23:59:59</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2021-10-22 09:00:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2021-10-28 23:59:59</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2021-11-12 09:00:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2021-11-18 23:59:59</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2022-02-11 00:00:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2022-02-17 23:59:59</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2022-03-18 00:00:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2022-03-24 23:59:59</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Binh phù gói quà</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2023-04-02 00:00:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2023-04-08 23:59:59</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2020-10-16 00:00:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2020-10-22 23:59:59</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2021-06-25 09:00:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2021-07-01 23:59:59</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2021-07-23 09:00:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2021-07-29 23:59:59</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2021-08-27 09:00:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2021-09-02 23:59:59</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2021-11-05 09:00:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2021-11-11 23:59:59</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2022-01-07 00:00:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2022-01-13 23:59:59</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2022-03-11 00:00:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2022-03-17 23:59:59</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mệnh ký gói quà</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2020-09-11 00:00:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2022-09-17 23:59:59</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cầu nguyện thương thành</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2020-12-18 00:00:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2020-12-24 23:59:59</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2021-01-15 00:00:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2021-01-21 23:59:59</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2021-02-19 00:00:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2021-02-25 23:59:59</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2021-03-26 09:00:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2021-04-01 23:59:59</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2021-04-23 09:00:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2021-04-29 23:59:59</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2021-05-21 09:00:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2021-05-27 23:59:59</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2021-06-18 09:00:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2021-06-24 23:59:59</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2021-07-09 09:00:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2021-07-15 23:59:59</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2021-08-20 09:00:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2021-08-26 23:59:59</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2021-09-24 09:00:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2021-09-30 23:59:59</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2021-10-15 09:00:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2021-10-21 23:59:59</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2022-02-18 00:00:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2022-02-24 23:59:59</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2022-04-01 00:00:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2022-04-07 23:59:59</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Khoa học kỹ thuật gói quà</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2020-10-23 00:00:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2020-11-05 23:59:59</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bọt nước gói quà</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2021-04-30 09:00:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2021-05-06 23:59:59</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pháo hoa gói quà</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ngọc bội gói quà</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thần Ma ghi chép gói quà</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2021-08-06 09:00:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2021-08-12 23:59:59</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2021-09-03 09:00:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2021-09-09 23:59:59</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Làn da trở lại nhà máy gói quà</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2022-04-08 00:00:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2022-04-14 23:59:59</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vượt phục mệnh ký gói quà</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2020-10-29 23:59:59</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2020-11-28 00:00:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2020-12-03 23:59:59</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2021-03-05 00:00:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2021-03-11 23:59:59</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2021-04-02 09:00:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2021-04-08 23:59:59</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2021-11-05 03:00:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2022-01-21 00:00:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2022-01-27 23:59:59</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2022-03-11 03:00:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vượt phục đúc lại gói quà</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2020-12-11 00:00:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2020-12-17 23:59:59</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2021-02-05 00:00:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2021-02-11 23:59:59</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2021-04-16 09:00:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2021-04-22 23:59:59</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2021-05-28 09:00:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2021-06-03 23:59:59</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2021-09-17 09:00:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2021-09-23 23:59:59</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2022-03-04 00:00:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2022-03-10 23:59:59</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2022-04-01 03:00:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mù hộp gói quà</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2020-12-14 23:59:59</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Đèn lồng gói quà</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2021-01-01 00:00:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2021-01-03 23:59:59</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hoa hồng gói quà</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2021-02-14 00:00:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2021-02-16 23:59:59</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nữ vương gói quà</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2021-03-07 00:00:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2021-03-09 23:59:59</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2021-06-20 23:59:59</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2021-10-22 00:00:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lễ Tạ Ơn gói quà</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2021-11-19 00:00:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2021-11-25 23:59:59</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chè trôi nước gói quà</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tiên Khí bên trên mới</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2021-12-31 00:00:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2022-01-06 23:59:59</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2022-02-04 00:00:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2022-03-25 00:00:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vượt phục thú hồn gói quà</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2021-01-08 00:00:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2021-01-14 23:59:59</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2021-10-08 00:00:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2021-10-14 23:59:59</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2021-12-13 03:00:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2022-02-25 03:00:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2022-03-03 23:59:59</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2023-04-16 03:00:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-03-31 23:59:59</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tuyết chi khánh điển</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hoa đào khánh điển</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2021-03-11 00:00:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tướng kế thừa gói quà</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Đồ cất giữ phong ấn gói quà</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2021-10-01 00:00:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2021-10-07 23:59:59</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2022-02-25 00:00:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tiên Khí kế thừa gói quà</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2021-07-14 00:00:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2021-08-24 23:59:59</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2021-10-29 00:00:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2021-11-04 23:59:59</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vượt phục long châu gói quà</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2022-01-14 00:00:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2022-01-20 23:59:59</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2022-02-18 03:00:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2022-03-18 03:00:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Khu ma thương thành</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2022-02-04 01:00:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2022-02-10 23:59:59</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trợ lực gói quà</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2021-11-19 09:00:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2022-11-25 23:59:59</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Biết võ kéo lên</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vượt phục tướng tiêu hao</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2020-12-10 00:00:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2022-12-16 23:59:59</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tỉ ấn thương thành</t>
+  </si>
+  <si>
+    <t xml:space="preserve">仙器ID</t>
+  </si>
+  <si>
+    <t xml:space="preserve">*备注</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0:1:3000#3:500041:30#3:100071:10#3:400036:1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">元宝*120,种族徽章自选*30,作战物资*10,低级附魔自选*1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0:1:300#3:500041:150#3:100071:60#3:400036:4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">元宝*300,种族徽章自选*150,作战物资*60,低级附魔自选*4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0:1:25000#3:500041:300#3:100071:100#3:400036:8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">元宝*500,种族徽章自选*300,作战物资*100,低级附魔自选*8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0:1:100000#3:500041:700#3:100071:240#3:400037:8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">元宝*1280,种族徽章自选*700,作战物资*240,中级附魔自选*8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0:1:200000#3:500041:1400#3:100071:500#3:400038:8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">元宝*3280,种族徽章自选*1400,作战物资*500,高级附魔自选*8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0:1:500000#3:500041:2800#3:100071:1000#3:400038:16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">元宝*6480,种族徽章自选*2800,作战物资*1000,高级附魔自选*16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0:1:3000#3:100073:10#3:100253:20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">元宝*120,兵符*10,强化石自选盒*1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0:1:25000#3:100073:20#3:100252:100#3:590005:3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">元宝*500,兵符*20,命签*3,强化石自选盒*3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0:1:100000#3:100073:50#3:100252:400#3:100253:400#3:100255:10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">元宝*1280,兵符*50,高级寻宝券*10,强化石自选盒*6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0:1:200000#3:100073:130#3:100258:20#3:100004:4000#0:0:20000000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">元宝*3280,兵符*130,命签*10,,强化石自选盒*18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0:1:500000#3:100073:250#3:500087:13000#0:0:5000000#0:4:50000000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">元宝*6480,兵符*250,高级寻宝券*30,强化石自选盒*40</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0:1:3000#3:100025:2#3:100006:1#3:1000001:1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">元宝*120,命签*2,高级寻宝券*1,金币袋(24小时)*1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0:1:300#3:100025:4#3:400036:8#3:1000001:2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">元宝*300,命签*4,低级附魔自选*8,金币袋(24小时)*2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0:1:100000#3:100025:10#3:400038:4#3:1000001:2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">元宝*1280,命签*10,高级附魔自选*4,金币袋(24小时)*2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0:1:200000#3:100025:20#3:400038:8#3:1000001:2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">元宝*3280,命签*20,高级附魔自选*8,金币袋(24小时)*2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0:1:500000#3:100025:35#3:400038:16#3:1000001:13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">元宝*6480,命签*35,高级附魔自选*16,金币袋(24小时)*13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0:1:3000#3:100077:2#3:100027:6#0:0:100000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">元宝*120,祈愿令*2,悬赏刷新券*6,金币*100000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0:1:300#3:100077:7#3:100001:300#0:0:1000000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">元宝*300,祈愿令*7,进阶石*300,金币*1000000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0:1:100000#3:100077:30#3:100001:1000#0:4:8000000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">元宝*1280,祈愿令*30,进阶石*1000,英雄经验*8000000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0:1:1980#3:100077:40#3:1000010:2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">元宝*1980,祈愿令*40,五星通用英魂*2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0:1:200000#3:100077:70#0:0:1000000#0:4:10000000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">元宝*3280,祈愿令*70,金币*10000000,英雄经验*10000000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0:1:200000#3:100077:75#3:1000010:3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">元宝*3280,祈愿令*75,五星通用英魂*3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0:1:500000#3:100077:150#0:0:3000000#0:4:30000000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">元宝*6480,祈愿令*150,金币*30000000,英雄经验*30000000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0:1:3000#3:100311:10#3:1000001:1#3:1000002:1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0:1:25000#3:100311:20#0:0:100000#3:100001:500</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0:1:100000#3:100311:50#0:0:500000#0:4:5000000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0:1:200000#3:100311:130#0:0:1000000#3:100001:1000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0:1:500000#3:100311:200#0:0:2000000#0:4:20000000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7:56000101:1#0:1:500000#3:100216:35000#0:0:2000000#3:100044:10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7:58000101:1#0:1:500000#3:100216:35000#0:0:2000000#3:100044:10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7:57000101:1#0:1:500000#3:100216:35000#0:0:2000000#3:100044:10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">沉香开山斧</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7:45000101:1#0:1:500000#3:100216:35000#0:0:2000000#3:100044:10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">三圣母宝莲灯</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0:1:3000#3:100004:1400#3:100022:10#3:1000001:2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0:1:25000#3:100004:6000#3:100025:3#3:1000001:3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0:1:100000#3:100004:14000#3:100025:7#3:1000001:4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0:1:200000#3:100004:3000#5:20001:1#3:1000001:7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0:1:500000#3:100004:7000#5:20001:2#3:1000001:15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0:1:60#3:100025:1#3:100022:10#3:100086:1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0:1:25000#3:1000010:1#3:100022:30#3:100086:2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0:1:100000#3:100216:14000#0:0:1000000#3:100086:6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0:1:200000#3:100025:15#3:200018:14000#3:100086:14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0:1:500000#3:500015:30#3:100022:80#3:100086:30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0:1:60#3:100025:1#3:200069:15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">元宝*60,命签*1,食材*15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0:1:25000#3:100025:3#3:100022:30#3:200069:50</t>
+  </si>
+  <si>
+    <t xml:space="preserve">元宝*500,命签*3,高级点将券*30,食材*45</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0:1:100000#3:100025:6#3:100004:15000#3:200069:120</t>
+  </si>
+  <si>
+    <t xml:space="preserve">元宝*1280,命签*6,鎏金粉*15000,食材*120</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0:1:500000#3:500015:25#0:0:3000000#3:200069:750</t>
+  </si>
+  <si>
+    <t xml:space="preserve">元宝*6480,灌魔之瓶自选*25,食材*750,金币*3000万</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0:1:500000#3:400018:1#3:20001:6#3:100511:50</t>
+  </si>
+  <si>
+    <t xml:space="preserve">元宝*6480,天级兽魂礼包*1,龙魂*6,火鸡奖券*50</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3:100059:1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0:1:680#3:100059:50#3:100031:100#6:30002:1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0:1:100000#3:100059:100#3:100031:200#6:30002:2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0:1:200000#3:100059:260#3:100031:300#6:30002:5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0:1:500000#3:100059:520#3:100031:400#6:30002:10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0:1:3000#3:100513:2#0:0:100000#0:4:1000000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">元宝*120,小雪人*2,金币*1000000,英雄经验*1000000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0:1:300#3:100513:10#0:0:500000#0:4:5000000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">元宝*300,小雪人*10,金币*5000000,英雄经验*5000000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0:1:100000#3:100513:30#0:0:1000000#0:4:10000000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">元宝*1280,小雪人*30,金币*10000000,英雄经验*10000000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0:1:200000#3:100513:70#0:0:2000000#0:4:20000000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">元宝*3280,小雪人*70,金币*20000000,英雄经验*20000000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0:1:500000#3:100513:150#0:0:3000000#0:4:30000000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">元宝*6480,小雪人*150,金币*30000000,英雄经验*30000000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0:1:3000#3:100513:2#0:0:50000#0:4:500000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">元宝*120,桃花酒*2,金币*500000,英雄经验*500000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0:1:300#3:100513:10#0:0:200000#0:4:2000000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">元宝*300,桃花酒*10,金币*2000000,英雄经验*2000000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0:1:100000#3:100513:30#0:0:500000#0:4:5000000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">元宝*1280,桃花酒*30,金币*5000000,英雄经验*5000000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0:1:200000#3:100513:70#0:0:1000000#0:4:10000000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">元宝*3280,桃花酒*70,金币*10000000,英雄经验*10000000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0:1:500000#3:100513:150#0:0:2000000#0:4:20000000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">元宝*6480,桃花酒*150,金币*20000000,英雄经验*20000000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3:200052:10#0:0:100000#0:4:1000000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">元神*10,金币*1000000,英雄经验*1000000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3:200053:5#0:0:100000#0:4:1000000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">金丹元神*5,金币*1000000,英雄经验*1000000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3:200052:30#0:0:300000#0:4:3000000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">元神*30,金币*3000000,英雄经验*3000000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3:200053:20#0:0:300000#0:4:3000000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">金丹元神*20,金币*3000000,英雄经验*3000000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3:200052:50#0:0:500000#0:4:5000000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">元神*50,金币*5000000,英雄经验*5000000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3:200053:35#0:0:500000#0:4:5000000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">金丹元神*35,金币*5000000,英雄经验*5000000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3:200052:85#0:0:1000000#0:4:10000000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">元神*85,金币*10000000,英雄经验*10000000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3:200053:60#0:0:1000000#0:4:10000000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">金丹元神*60,金币*10000000,英雄经验*10000000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3:200052:170#0:0:2000000#0:4:20000000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">元神*170,金币*20000000,英雄经验*20000000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3:200053:120#0:0:2000000#0:4:20000000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">金丹元神*120,金币*20000000,英雄经验*20000000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3:200057:5#0:0:100000#0:4:1000000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3:200057:20#0:0:300000#0:4:3000000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3:200057:35#0:0:500000#0:4:5000000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3:200057:60#0:0:1000000#0:4:10000000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3:200057:120#0:0:2000000#0:4:20000000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3:200054:10#3:100098:200#0:0:5000000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3:200054:20#3:100098:500#0:0:10000000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3:200054:40#3:100098:1000#0:0:20000000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3:200055:400</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3:200055:9800#0:0:300000#0:4:3000000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3:200055:32800#0:0:1000000#0:4:10000000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3:200055:64800#0:0:2000000#0:4:20000000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0:1:300#3:100098:200#0:0:200000#0:4:2000000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0:1:100000#3:100098:800#0:0:500000#0:4:5000000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0:1:200000#3:100098:2400#0:0:1000000#0:4:10000000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0:1:500000#3:100098:4800#0:0:2000000#0:4:20000000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0:1:60#3:100004:1500#5:3:1#3:100022:3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">元宝*60,鎏金粉*1500,白泽印*1,高级点将券*3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0:1:25000#3:400016:3#3:400017:1#0:4:3000000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">元宝*400,鎏金粉大礼包*3,随机篆印礼包*1,英雄经验*3000000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0:1:100000#3:400016:7#5:4:2#0:4:8000000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">元宝*1200,鎏金粉大礼包*7,玄武印*2,英雄经验*8000000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0:1:1980#3:400016:10#3:500011:1#3:400017:1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">元宝*1800,鎏金粉大礼包*10,篆印自选礼包*1,随机篆印礼包*1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0:1:200000#3:400016:18#3:500011:2#5:20001:3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">元宝*3000,鎏金粉大礼包*18,篆印自选礼包*2,龙魂*5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0:1:500000#3:560003:1#3:100004:4000#0:4:2500000#5:20001:10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">元宝*6000,龙雀印*1,鎏金粉*40000,英雄经验*25000000,龙魂*10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3:590024:1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3:590020:1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0:1:3000#3:590020:6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">元宝*120,魔怪悬赏令*6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0:1:300#3:590021:1#3:590020:3#3:100027:6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">元宝*300,驱魔师直升券*1,魔怪悬赏令*3,悬赏刷新令*6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0:1:100000#3:590024:40#3:590020:30#3:100027:15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">元宝*1280,小熊软糖*40,魔怪悬赏令*30,悬赏刷新令*15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0:1:1980#3:590021:2#3:590024:100#3:590020:35</t>
+  </si>
+  <si>
+    <t xml:space="preserve">元宝*1980,驱魔师直升券*2,小熊软糖*100,魔怪悬赏令*35</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0:1:200000#3:590021:5#3:590020:80#3:100027:35</t>
+  </si>
+  <si>
+    <t xml:space="preserve">元宝*3280,驱魔师直升券*5,魔怪悬赏令*80,悬赏刷新令*35</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0:1:500000#3:590021:10#3:590024:300#3:590020:150</t>
+  </si>
+  <si>
+    <t xml:space="preserve">元宝*6480,驱魔师直升券*10,魔怪悬赏令*160,小熊软糖*300</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3:100004:1000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">鎏金粉*1000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3:100006:3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">高级寻宝券*3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3:100022:10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">高级点将券*10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0:1:240#3:100025:1#3:100004:1500#3:100044:2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">元宝*240,命签*1,鎏金粉*1500,精英点将券*2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0:1:240#3:100027:10#3:100004:1500#3:100044:2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">元宝*240,悬赏刷新券*10,鎏金粉*1500,精英点将券*2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0:1:240#3:100022:10#3:100004:1500#3:100044:2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">元宝*240,高级点将券*10,鎏金粉*1500,精英点将券*2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0:1:1500#3:100077:20#3:590015:5#3:1000010:1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">元宝*1500,祈愿令*20,会武材料盒*5,5星通用英魂*1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0:1:1500#3:590016:1#3:590015:5#3:100044:10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">元宝*1500,金丹元神自选*1,会武材料盒*5,精英点将券*10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0:1:1500#3:200054:10#3:590015:5#3:100098:200</t>
+  </si>
+  <si>
+    <t xml:space="preserve">元宝*1500,乾坤玉*10,会武材料盒*5,龙珠*200</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0:1:1500#3:200055:9800#3:590015:5#3:100089:20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">元宝*1500,补天残片*9800,会武材料盒*5,宝箱秘钥*20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0:1:1500#3:500011:2#3:590015:5#3:100004:5000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">元宝*1500,篆印自选礼包*2,会武材料盒*5,鎏金粉*5000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0:1:1500#3:400038:4#3:590015:5#3:100022:20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">元宝*1500,高级附魔自选*4,会武材料盒*5,高级点将券*20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0:1:9800#5:20001:15#3:590015:20#3:400038:16#3:100004:30000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">元宝*9800,龙魂*15,会武材料盒*20,高级附魔自选*16,鎏金粉*30000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0:1:9800#3:500014:1#3:590015:20#6:30002:5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">元宝*9800,天级兽魂自选*1,会武材料盒*20,兽魂经验(大)*5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0:1:9800#3:401001:1#3:590015:20#3:100305:3000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">元宝*9800,神装自选礼包*1,会武材料盒*20,神装精铁*3000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">兑换分组</t>
+  </si>
+  <si>
+    <t xml:space="preserve">标签名</t>
+  </si>
+  <si>
+    <t xml:space="preserve">展示道具</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trung thu đoàn viên</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2020-10-01 00:00:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2021-10-08 23:59:59</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Năm nhân # Trăm quả # Lòng đỏ trứng # Chà bông # Hi hữu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100078#100079#100080#100081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thuốc nhuộm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2020-11-27 00:00:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2021-10-08 23:59:60</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lá phong đỏ # Lá dâu lục # Hạnh lá hoàng # Hi hữu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100093#100094#100095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tâm nguyện bình</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2023-04-23 00:00:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-12-29 23:59:61</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tướng # Cao cấp vật liệu # Vật liệu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chè trôi nước</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2021-10-08 23:59:62</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bánh đậu chè trôi nước # Hạt vừng chè trôi nước # Thịt tươi chè trôi nước # Tử khoai chè trôi nước # Hi hữu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100238#100239#100240#100241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hoa cỏ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2021-10-08 23:59:63</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hồ Điệp Lan # Hoa nhài # Hoa thủy tiên # Hoa bách hợp # Hi hữu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100246#100247#100248#100249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Khu ma</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2021-10-08 23:59:64</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Khu ma giá trị</t>
+  </si>
+  <si>
+    <t xml:space="preserve">限购</t>
+  </si>
+  <si>
+    <t xml:space="preserve">消耗</t>
+  </si>
+  <si>
+    <t xml:space="preserve">是否显示兑换红点</t>
+  </si>
+  <si>
+    <t xml:space="preserve">类型</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3:100078:200</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5星随机碎片*50</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4:606008:50</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3:100078:250</t>
+  </si>
+  <si>
+    <t xml:space="preserve">人</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4:606009:50</t>
+  </si>
+  <si>
+    <t xml:space="preserve">仙</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4:606010:50</t>
+  </si>
+  <si>
+    <t xml:space="preserve">妖</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4:606011:50</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3:100078:500</t>
+  </si>
+  <si>
+    <t xml:space="preserve">神</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4:606012:50</t>
+  </si>
+  <si>
+    <t xml:space="preserve">魔</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3:100001:10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3:100079:1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">进阶石*10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3:100002:10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3:100079:15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">太乙精金*10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0:0:50000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">金币*50000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0:4:10000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">经验*10000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3:100025:1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3:100080:100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">先祖水晶</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3:100022:1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3:100080:10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">高级点将券</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3:100006:1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3:100080:50</t>
+  </si>
+  <si>
+    <t xml:space="preserve">高级寻宝券</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3:100005:1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3:100080:5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">寻宝券</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3:100212:1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3:100081:10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">玄铁</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3:100213:1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3:100081:100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">神铁</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3:100214:1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">陨铁精华</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3:700006:1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3:100078:1500#3:100079:1500</t>
+  </si>
+  <si>
+    <t xml:space="preserve">后羿皮肤</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3:700007:1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3:100080:1500#3:100081:1500</t>
+  </si>
+  <si>
+    <t xml:space="preserve">嫦娥皮肤</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3:900023:1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3:100078:1000#3:100079:1000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">春华秋实</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3:900024:1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3:100080:1000#3:100081:1000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">五谷丰登</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3:100093:300</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3:100093:400</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3:100093:700</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3:100094:30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3:100094:150</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3:100094:20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3:100095:200</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3:100095:40</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3:100095:10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3:800022:1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3:100093:700#3:100094:700#3:100095:700</t>
+  </si>
+  <si>
+    <t xml:space="preserve">头像框</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3:700012:1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3:100093:1000#3:100094:1000#3:100095:1000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">黄泉皮肤</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3:100099:10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3:100099:15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3:100099:1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3:100099:150</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3:100099:20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3:100099:100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3:100099:5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3:100099:500</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3:100099:600</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3:100099:800</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3:100238:200</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3:100238:250</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3:100238:500</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3:100239:1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3:100239:15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3:100240:100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3:100240:10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3:100240:50</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3:100240:5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3:100241:10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3:100241:100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3:700010:1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3:100238:1500#3:100239:1500</t>
+  </si>
+  <si>
+    <t xml:space="preserve">鲲皮肤</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3:700016:1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3:100240:1500#3:100241:1500</t>
+  </si>
+  <si>
+    <t xml:space="preserve">夜魅皮肤</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3:100238:1000#3:100239:1000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3:100240:1000#3:100241:1000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3:100246:200</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3:100246:250</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3:100246:500</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3:100247:1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3:100247:15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3:100248:100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3:100248:10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3:100248:50</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3:100248:5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3:100249:10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3:100249:100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3:700018:1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3:100246:1500#3:100247:1500</t>
+  </si>
+  <si>
+    <t xml:space="preserve">醒狮</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3:700009:1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3:100248:1500#3:100249:1500</t>
+  </si>
+  <si>
+    <t xml:space="preserve">几何数论</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3:800033:1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3:100246:1000#3:100247:1000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">玫瑰芬芳</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4:608003:50</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3:100099:6500</t>
+  </si>
+  <si>
+    <t xml:space="preserve">光*1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4:602026:50</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3:100099:5000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">土地*50</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4:604019:50</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3:100099:4500</t>
+  </si>
+  <si>
+    <t xml:space="preserve">西王母*50</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4:604010:50</t>
+  </si>
+  <si>
+    <t xml:space="preserve">玉帝*50</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4:605008:50</t>
+  </si>
+  <si>
+    <t xml:space="preserve">刑天*50</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4:605013:50</t>
+  </si>
+  <si>
+    <t xml:space="preserve">烛龙*50</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4:602023:50</t>
+  </si>
+  <si>
+    <t xml:space="preserve">九天玄女*50</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4:601020:50</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3:100099:3000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">哪吒*50</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4:603022:50</t>
+  </si>
+  <si>
+    <t xml:space="preserve">妲己*50</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4:602018:50</t>
+  </si>
+  <si>
+    <t xml:space="preserve">斗战胜佛*50</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4:603024:50</t>
+  </si>
+  <si>
+    <t xml:space="preserve">曼珠*50</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4:602024:50</t>
+  </si>
+  <si>
+    <t xml:space="preserve">玄奘*50</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4:601017:50</t>
+  </si>
+  <si>
+    <t xml:space="preserve">后羿*50</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3:100099:1000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5星神族碎片*50</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5星魔族碎片*50</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3:100099:400</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7:55000101:1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">信仰*1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3:500026:1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">专属仙器自选*1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3:580001:1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">兽灵自选礼包*1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3:500014:1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">天级兽魂自选*1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3:100228:1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3:100099:4000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">生肖令*1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5:20001:5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3:100099:3500</t>
+  </si>
+  <si>
+    <t xml:space="preserve">龙魂*5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6:30002:2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">兽魂经验(大)*2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3:1200016:1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">雪花标志</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3:500011:1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">篆印自选礼包*1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0:0:100000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">金币*100000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0:4:50000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">英雄经验*50000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3:100099:300</t>
+  </si>
+  <si>
+    <t xml:space="preserve">高级寻宝券*1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">命签*1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3:590001:1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3:100099:450</t>
+  </si>
+  <si>
+    <t xml:space="preserve">幼龙自选*1</t>
+  </si>
+  <si>
     <t xml:space="preserve">兽灵精华*10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3:100255:1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">兽灵技能书*1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3:100253:10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">布偶*10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0:1:450#3:300045:1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">元宝*450,兽灵助力礼包*1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0:1:980#3:100252:100#3:590008:1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">元宝*980,兽灵精华*100,好运红包*1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0:1:1980#3:100252:100#3:100098:1000#3:590008:2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">元宝*1980,兽灵精华*100,龙珠*1000,好运红包*2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4:606002:50</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5星随机碎片*50</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3:100023:5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">演武场挑战券*5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0:1:450#4:606002:50</t>
-  </si>
-  <si>
-    <t xml:space="preserve">元宝*450,5星随机碎片*50</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0:1:980#3:100044:15#3:590012:4#3:590008:1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">元宝*980,精英点将券*15,高级演武礼包*4,好运红包*1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0:1:1980#3:100044:30#3:590012:10#3:590008:2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">元宝*1980,精英点将券*30,高级演武礼包*10,好运红包*2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3:100004:1500</t>
-  </si>
-  <si>
-    <t xml:space="preserve">鎏金粉*1500</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3:100006:4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">高级寻宝券*4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0:1:450#3:100006:10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">元宝*450,高级寻宝券*10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0:1:980#3:100004:8000#3:100006:10#3:590008:1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">元宝*980,鎏金粉*8000,高级寻宝券*10,好运红包*1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0:1:1980#3:100004:16000#3:100006:30#3:590008:2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">元宝*1980,鎏金粉*16000,高级寻宝券*30,好运红包*2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">开服天数</t>
-  </si>
-  <si>
-    <t xml:space="preserve">活动期间达标开启</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vật tư thương thành</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2020-08-21 00:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2020-08-27 23:59:59</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2020-10-09 00:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2020-10-15 23:59:59</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2020-11-20 00:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2020-11-26 23:59:59</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2020-12-25 00:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2020-12-31 23:59:59</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2021-01-29 00:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2021-02-04 23:59:59</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2021-03-12 00:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2021-03-18 23:59:59</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2021-04-09 09:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2021-04-15 23:59:59</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2021-05-07 09:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2021-05-13 23:59:59</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2021-06-04 09:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2021-06-10 23:59:59</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2021-07-02 09:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2021-07-08 23:59:59</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2021-07-30 09:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2021-08-05 23:59:59</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2021-09-10 09:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2021-09-16 23:59:59</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2021-10-22 09:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2021-10-28 23:59:59</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2021-11-12 09:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2021-11-18 23:59:59</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2022-02-11 00:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2022-02-17 23:59:59</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2022-03-18 00:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2022-03-24 23:59:59</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Binh phù gói quà</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2023-04-02 00:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2023-04-08 23:59:59</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2020-10-16 00:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2020-10-22 23:59:59</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2021-06-25 09:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2021-07-01 23:59:59</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2021-07-23 09:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2021-07-29 23:59:59</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2021-08-27 09:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2021-09-02 23:59:59</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2021-11-05 09:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2021-11-11 23:59:59</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2022-01-07 00:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2022-01-13 23:59:59</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2022-03-11 00:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2022-03-17 23:59:59</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mệnh ký gói quà</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2020-09-11 00:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2022-09-17 23:59:59</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cầu nguyện thương thành</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2020-12-18 00:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2020-12-24 23:59:59</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2021-01-15 00:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2021-01-21 23:59:59</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2021-02-19 00:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2021-02-25 23:59:59</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2021-03-26 09:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2021-04-01 23:59:59</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2021-04-23 09:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2021-04-29 23:59:59</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2021-05-21 09:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2021-05-27 23:59:59</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2021-06-18 09:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2021-06-24 23:59:59</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2021-07-09 09:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2021-07-15 23:59:59</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2021-08-20 09:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2021-08-26 23:59:59</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2021-09-24 09:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2021-09-30 23:59:59</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2021-10-15 09:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2021-10-21 23:59:59</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2022-02-18 00:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2022-02-24 23:59:59</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2022-04-01 00:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2022-04-07 23:59:59</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Khoa học kỹ thuật gói quà</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2020-10-23 00:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2020-11-05 23:59:59</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bọt nước gói quà</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2021-04-30 09:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2021-05-06 23:59:59</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pháo hoa gói quà</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ngọc bội gói quà</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thần Ma ghi chép gói quà</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2021-08-06 09:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2021-08-12 23:59:59</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2021-09-03 09:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2021-09-09 23:59:59</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Làn da trở lại nhà máy gói quà</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2022-04-08 00:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2022-04-14 23:59:59</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vượt phục mệnh ký gói quà</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2020-10-29 23:59:59</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2020-11-28 00:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2020-12-03 23:59:59</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2021-03-05 00:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2021-03-11 23:59:59</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2021-04-02 09:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2021-04-08 23:59:59</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2021-11-05 03:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2022-01-21 00:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2022-01-27 23:59:59</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2022-03-11 03:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vượt phục đúc lại gói quà</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2020-12-11 00:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2020-12-17 23:59:59</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2021-02-05 00:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2021-02-11 23:59:59</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2021-04-16 09:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2021-04-22 23:59:59</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2021-05-28 09:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2021-06-03 23:59:59</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2021-09-17 09:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2021-09-23 23:59:59</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2022-03-04 00:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2022-03-10 23:59:59</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2022-04-01 03:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mù hộp gói quà</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2020-12-14 23:59:59</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Đèn lồng gói quà</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2021-01-01 00:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2021-01-03 23:59:59</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hoa hồng gói quà</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2021-02-14 00:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2021-02-16 23:59:59</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nữ vương gói quà</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2021-03-07 00:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2021-03-09 23:59:59</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2021-06-20 23:59:59</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2021-10-22 00:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lễ Tạ Ơn gói quà</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2021-11-19 00:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2021-11-25 23:59:59</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chè trôi nước gói quà</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tiên Khí bên trên mới</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2021-12-31 00:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2022-01-06 23:59:59</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2022-02-04 00:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2022-03-25 00:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vượt phục thú hồn gói quà</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2021-01-08 00:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2021-01-14 23:59:59</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2021-10-08 00:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2021-10-14 23:59:59</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2021-12-13 03:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2022-02-25 03:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2022-03-03 23:59:59</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2023-04-16 03:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-03-31 23:59:59</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tuyết chi khánh điển</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hoa đào khánh điển</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2021-03-11 00:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tướng kế thừa gói quà</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Đồ cất giữ phong ấn gói quà</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2021-10-01 00:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2021-10-07 23:59:59</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2022-02-25 00:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tiên Khí kế thừa gói quà</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2021-07-14 00:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2021-08-24 23:59:59</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2021-10-29 00:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2021-11-04 23:59:59</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vượt phục long châu gói quà</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2022-01-14 00:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2022-01-20 23:59:59</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2022-02-18 03:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2022-03-18 03:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Khu ma thương thành</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2022-02-04 01:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2022-02-10 23:59:59</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trợ lực gói quà</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2021-11-19 09:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2022-11-25 23:59:59</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Biết võ kéo lên</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vượt phục tướng tiêu hao</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2020-12-10 00:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2022-12-16 23:59:59</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tỉ ấn thương thành</t>
-  </si>
-  <si>
-    <t xml:space="preserve">仙器ID</t>
-  </si>
-  <si>
-    <t xml:space="preserve">*备注</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0:1:3000#3:500041:30#3:100071:10#3:400036:1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">元宝*120,种族徽章自选*30,作战物资*10,低级附魔自选*1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0:1:300#3:500041:150#3:100071:60#3:400036:4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">元宝*300,种族徽章自选*150,作战物资*60,低级附魔自选*4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0:1:25000#3:500041:300#3:100071:100#3:400036:8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">元宝*500,种族徽章自选*300,作战物资*100,低级附魔自选*8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0:1:100000#3:500041:700#3:100071:240#3:400037:8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">元宝*1280,种族徽章自选*700,作战物资*240,中级附魔自选*8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0:1:200000#3:500041:1400#3:100071:500#3:400038:8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">元宝*3280,种族徽章自选*1400,作战物资*500,高级附魔自选*8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0:1:500000#3:500041:2800#3:100071:1000#3:400038:16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">元宝*6480,种族徽章自选*2800,作战物资*1000,高级附魔自选*16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0:1:3000#3:100073:10#3:100253:20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">元宝*120,兵符*10,强化石自选盒*1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0:1:25000#3:100073:20#3:100252:100#3:590005:3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">元宝*500,兵符*20,命签*3,强化石自选盒*3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0:1:100000#3:100073:50#3:100252:400#3:100253:400#3:100255:10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">元宝*1280,兵符*50,高级寻宝券*10,强化石自选盒*6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0:1:200000#3:100073:130#3:100258:20#3:100004:4000#0:0:20000000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">元宝*3280,兵符*130,命签*10,,强化石自选盒*18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0:1:500000#3:100073:250#3:500087:13000#0:0:5000000#0:4:50000000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">元宝*6480,兵符*250,高级寻宝券*30,强化石自选盒*40</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0:1:3000#3:100025:2#3:100006:1#3:1000001:1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">元宝*120,命签*2,高级寻宝券*1,金币袋(24小时)*1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0:1:300#3:100025:4#3:400036:8#3:1000001:2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">元宝*300,命签*4,低级附魔自选*8,金币袋(24小时)*2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0:1:100000#3:100025:10#3:400038:4#3:1000001:2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">元宝*1280,命签*10,高级附魔自选*4,金币袋(24小时)*2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0:1:200000#3:100025:20#3:400038:8#3:1000001:2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">元宝*3280,命签*20,高级附魔自选*8,金币袋(24小时)*2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0:1:500000#3:100025:35#3:400038:16#3:1000001:13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">元宝*6480,命签*35,高级附魔自选*16,金币袋(24小时)*13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0:1:3000#3:100077:2#3:100027:6#0:0:100000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">元宝*120,祈愿令*2,悬赏刷新券*6,金币*100000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0:1:300#3:100077:7#3:100001:300#0:0:1000000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">元宝*300,祈愿令*7,进阶石*300,金币*1000000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0:1:100000#3:100077:30#3:100001:1000#0:4:8000000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">元宝*1280,祈愿令*30,进阶石*1000,英雄经验*8000000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0:1:1980#3:100077:40#3:1000010:2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">元宝*1980,祈愿令*40,五星通用英魂*2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0:1:200000#3:100077:70#0:0:1000000#0:4:10000000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">元宝*3280,祈愿令*70,金币*10000000,英雄经验*10000000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0:1:200000#3:100077:75#3:1000010:3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">元宝*3280,祈愿令*75,五星通用英魂*3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0:1:500000#3:100077:150#0:0:3000000#0:4:30000000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">元宝*6480,祈愿令*150,金币*30000000,英雄经验*30000000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0:1:3000#3:100311:10#3:1000001:1#3:1000002:1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0:1:25000#3:100311:20#0:0:100000#3:100001:500</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0:1:100000#3:100311:50#0:0:500000#0:4:5000000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0:1:200000#3:100311:130#0:0:1000000#3:100001:1000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0:1:500000#3:100311:200#0:0:2000000#0:4:20000000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7:56000101:1#0:1:500000#3:100216:35000#0:0:2000000#3:100044:10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7:58000101:1#0:1:500000#3:100216:35000#0:0:2000000#3:100044:10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7:57000101:1#0:1:500000#3:100216:35000#0:0:2000000#3:100044:10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">沉香开山斧</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7:45000101:1#0:1:500000#3:100216:35000#0:0:2000000#3:100044:10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">三圣母宝莲灯</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0:1:3000#3:100004:1400#3:100022:10#3:1000001:2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0:1:25000#3:100004:6000#3:100025:3#3:1000001:3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0:1:100000#3:100004:14000#3:100025:7#3:1000001:4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0:1:200000#3:100004:3000#5:20001:1#3:1000001:7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0:1:500000#3:100004:7000#5:20001:2#3:1000001:15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0:1:60#3:100025:1#3:100022:10#3:100086:1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0:1:25000#3:1000010:1#3:100022:30#3:100086:2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0:1:100000#3:100216:14000#0:0:1000000#3:100086:6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0:1:200000#3:100025:15#3:200018:14000#3:100086:14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0:1:500000#3:500015:30#3:100022:80#3:100086:30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0:1:60#3:100025:1#3:200069:15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">元宝*60,命签*1,食材*15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0:1:25000#3:100025:3#3:100022:30#3:200069:50</t>
-  </si>
-  <si>
-    <t xml:space="preserve">元宝*500,命签*3,高级点将券*30,食材*45</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0:1:100000#3:100025:6#3:100004:15000#3:200069:120</t>
-  </si>
-  <si>
-    <t xml:space="preserve">元宝*1280,命签*6,鎏金粉*15000,食材*120</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0:1:500000#3:500015:25#0:0:3000000#3:200069:750</t>
-  </si>
-  <si>
-    <t xml:space="preserve">元宝*6480,灌魔之瓶自选*25,食材*750,金币*3000万</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0:1:500000#3:400018:1#3:20001:6#3:100511:50</t>
-  </si>
-  <si>
-    <t xml:space="preserve">元宝*6480,天级兽魂礼包*1,龙魂*6,火鸡奖券*50</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3:100059:1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0:1:680#3:100059:50#3:100031:100#6:30002:1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0:1:100000#3:100059:100#3:100031:200#6:30002:2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0:1:200000#3:100059:260#3:100031:300#6:30002:5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0:1:500000#3:100059:520#3:100031:400#6:30002:10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0:1:3000#3:100513:2#0:0:100000#0:4:1000000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">元宝*120,小雪人*2,金币*1000000,英雄经验*1000000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0:1:300#3:100513:10#0:0:500000#0:4:5000000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">元宝*300,小雪人*10,金币*5000000,英雄经验*5000000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0:1:100000#3:100513:30#0:0:1000000#0:4:10000000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">元宝*1280,小雪人*30,金币*10000000,英雄经验*10000000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0:1:200000#3:100513:70#0:0:2000000#0:4:20000000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">元宝*3280,小雪人*70,金币*20000000,英雄经验*20000000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0:1:500000#3:100513:150#0:0:3000000#0:4:30000000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">元宝*6480,小雪人*150,金币*30000000,英雄经验*30000000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0:1:3000#3:100513:2#0:0:50000#0:4:500000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">元宝*120,桃花酒*2,金币*500000,英雄经验*500000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0:1:300#3:100513:10#0:0:200000#0:4:2000000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">元宝*300,桃花酒*10,金币*2000000,英雄经验*2000000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0:1:100000#3:100513:30#0:0:500000#0:4:5000000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">元宝*1280,桃花酒*30,金币*5000000,英雄经验*5000000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0:1:200000#3:100513:70#0:0:1000000#0:4:10000000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">元宝*3280,桃花酒*70,金币*10000000,英雄经验*10000000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0:1:500000#3:100513:150#0:0:2000000#0:4:20000000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">元宝*6480,桃花酒*150,金币*20000000,英雄经验*20000000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3:200052:10#0:0:100000#0:4:1000000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">元神*10,金币*1000000,英雄经验*1000000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3:200053:5#0:0:100000#0:4:1000000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">金丹元神*5,金币*1000000,英雄经验*1000000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3:200052:30#0:0:300000#0:4:3000000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">元神*30,金币*3000000,英雄经验*3000000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3:200053:20#0:0:300000#0:4:3000000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">金丹元神*20,金币*3000000,英雄经验*3000000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3:200052:50#0:0:500000#0:4:5000000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">元神*50,金币*5000000,英雄经验*5000000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3:200053:35#0:0:500000#0:4:5000000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">金丹元神*35,金币*5000000,英雄经验*5000000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3:200052:85#0:0:1000000#0:4:10000000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">元神*85,金币*10000000,英雄经验*10000000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3:200053:60#0:0:1000000#0:4:10000000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">金丹元神*60,金币*10000000,英雄经验*10000000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3:200052:170#0:0:2000000#0:4:20000000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">元神*170,金币*20000000,英雄经验*20000000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3:200053:120#0:0:2000000#0:4:20000000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">金丹元神*120,金币*20000000,英雄经验*20000000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3:200057:5#0:0:100000#0:4:1000000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3:200057:20#0:0:300000#0:4:3000000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3:200057:35#0:0:500000#0:4:5000000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3:200057:60#0:0:1000000#0:4:10000000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3:200057:120#0:0:2000000#0:4:20000000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3:200054:10#3:100098:200#0:0:5000000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3:200054:20#3:100098:500#0:0:10000000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3:200054:40#3:100098:1000#0:0:20000000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3:200055:400</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3:200055:9800#0:0:300000#0:4:3000000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3:200055:32800#0:0:1000000#0:4:10000000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3:200055:64800#0:0:2000000#0:4:20000000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0:1:300#3:100098:200#0:0:200000#0:4:2000000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0:1:100000#3:100098:800#0:0:500000#0:4:5000000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0:1:200000#3:100098:2400#0:0:1000000#0:4:10000000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0:1:500000#3:100098:4800#0:0:2000000#0:4:20000000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0:1:60#3:100004:1500#5:3:1#3:100022:3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">元宝*60,鎏金粉*1500,白泽印*1,高级点将券*3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0:1:25000#3:400016:3#3:400017:1#0:4:3000000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">元宝*400,鎏金粉大礼包*3,随机篆印礼包*1,英雄经验*3000000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0:1:100000#3:400016:7#5:4:2#0:4:8000000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">元宝*1200,鎏金粉大礼包*7,玄武印*2,英雄经验*8000000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0:1:1980#3:400016:10#3:500011:1#3:400017:1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">元宝*1800,鎏金粉大礼包*10,篆印自选礼包*1,随机篆印礼包*1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0:1:200000#3:400016:18#3:500011:2#5:20001:3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">元宝*3000,鎏金粉大礼包*18,篆印自选礼包*2,龙魂*5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0:1:500000#3:560003:1#3:100004:4000#0:4:2500000#5:20001:10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">元宝*6000,龙雀印*1,鎏金粉*40000,英雄经验*25000000,龙魂*10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3:590024:1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3:590020:1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0:1:3000#3:590020:6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">元宝*120,魔怪悬赏令*6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0:1:300#3:590021:1#3:590020:3#3:100027:6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">元宝*300,驱魔师直升券*1,魔怪悬赏令*3,悬赏刷新令*6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0:1:100000#3:590024:40#3:590020:30#3:100027:15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">元宝*1280,小熊软糖*40,魔怪悬赏令*30,悬赏刷新令*15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0:1:1980#3:590021:2#3:590024:100#3:590020:35</t>
-  </si>
-  <si>
-    <t xml:space="preserve">元宝*1980,驱魔师直升券*2,小熊软糖*100,魔怪悬赏令*35</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0:1:200000#3:590021:5#3:590020:80#3:100027:35</t>
-  </si>
-  <si>
-    <t xml:space="preserve">元宝*3280,驱魔师直升券*5,魔怪悬赏令*80,悬赏刷新令*35</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0:1:500000#3:590021:10#3:590024:300#3:590020:150</t>
-  </si>
-  <si>
-    <t xml:space="preserve">元宝*6480,驱魔师直升券*10,魔怪悬赏令*160,小熊软糖*300</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3:100004:1000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">鎏金粉*1000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3:100006:3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">高级寻宝券*3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3:100022:10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">高级点将券*10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0:1:240#3:100025:1#3:100004:1500#3:100044:2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">元宝*240,命签*1,鎏金粉*1500,精英点将券*2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0:1:240#3:100027:10#3:100004:1500#3:100044:2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">元宝*240,悬赏刷新券*10,鎏金粉*1500,精英点将券*2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0:1:240#3:100022:10#3:100004:1500#3:100044:2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">元宝*240,高级点将券*10,鎏金粉*1500,精英点将券*2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0:1:1500#3:100077:20#3:590015:5#3:1000010:1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">元宝*1500,祈愿令*20,会武材料盒*5,5星通用英魂*1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0:1:1500#3:590016:1#3:590015:5#3:100044:10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">元宝*1500,金丹元神自选*1,会武材料盒*5,精英点将券*10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0:1:1500#3:200054:10#3:590015:5#3:100098:200</t>
-  </si>
-  <si>
-    <t xml:space="preserve">元宝*1500,乾坤玉*10,会武材料盒*5,龙珠*200</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0:1:1500#3:200055:9800#3:590015:5#3:100089:20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">元宝*1500,补天残片*9800,会武材料盒*5,宝箱秘钥*20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0:1:1500#3:500011:2#3:590015:5#3:100004:5000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">元宝*1500,篆印自选礼包*2,会武材料盒*5,鎏金粉*5000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0:1:1500#3:400038:4#3:590015:5#3:100022:20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">元宝*1500,高级附魔自选*4,会武材料盒*5,高级点将券*20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0:1:9800#5:20001:15#3:590015:20#3:400038:16#3:100004:30000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">元宝*9800,龙魂*15,会武材料盒*20,高级附魔自选*16,鎏金粉*30000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0:1:9800#3:500014:1#3:590015:20#6:30002:5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">元宝*9800,天级兽魂自选*1,会武材料盒*20,兽魂经验(大)*5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0:1:9800#3:401001:1#3:590015:20#3:100305:3000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">元宝*9800,神装自选礼包*1,会武材料盒*20,神装精铁*3000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">兑换分组</t>
-  </si>
-  <si>
-    <t xml:space="preserve">标签名</t>
-  </si>
-  <si>
-    <t xml:space="preserve">展示道具</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trung thu đoàn viên</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2020-10-01 00:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2021-10-08 23:59:59</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Năm nhân # Trăm quả # Lòng đỏ trứng # Chà bông # Hi hữu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100078#100079#100080#100081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thuốc nhuộm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2020-11-27 00:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2021-10-08 23:59:60</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lá phong đỏ # Lá dâu lục # Hạnh lá hoàng # Hi hữu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100093#100094#100095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tâm nguyện bình</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2023-04-23 00:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-12-29 23:59:61</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tướng # Cao cấp vật liệu # Vật liệu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chè trôi nước</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2021-10-08 23:59:62</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bánh đậu chè trôi nước # Hạt vừng chè trôi nước # Thịt tươi chè trôi nước # Tử khoai chè trôi nước # Hi hữu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100238#100239#100240#100241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hoa cỏ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2021-10-08 23:59:63</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hồ Điệp Lan # Hoa nhài # Hoa thủy tiên # Hoa bách hợp # Hi hữu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100246#100247#100248#100249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Khu ma</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2021-10-08 23:59:64</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Khu ma giá trị</t>
-  </si>
-  <si>
-    <t xml:space="preserve">限购</t>
-  </si>
-  <si>
-    <t xml:space="preserve">消耗</t>
-  </si>
-  <si>
-    <t xml:space="preserve">是否显示兑换红点</t>
-  </si>
-  <si>
-    <t xml:space="preserve">类型</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3:100078:200</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4:606008:50</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3:100078:250</t>
-  </si>
-  <si>
-    <t xml:space="preserve">人</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4:606009:50</t>
-  </si>
-  <si>
-    <t xml:space="preserve">仙</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4:606010:50</t>
-  </si>
-  <si>
-    <t xml:space="preserve">妖</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4:606011:50</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3:100078:500</t>
-  </si>
-  <si>
-    <t xml:space="preserve">神</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4:606012:50</t>
-  </si>
-  <si>
-    <t xml:space="preserve">魔</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3:100001:10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3:100079:1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">进阶石*10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3:100002:10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3:100079:15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">太乙精金*10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0:0:50000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">金币*50000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0:4:10000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">经验*10000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3:100025:1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3:100080:100</t>
-  </si>
-  <si>
-    <t xml:space="preserve">先祖水晶</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3:100022:1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3:100080:10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">高级点将券</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3:100006:1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3:100080:50</t>
-  </si>
-  <si>
-    <t xml:space="preserve">高级寻宝券</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3:100005:1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3:100080:5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">寻宝券</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3:100212:1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3:100081:10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">玄铁</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3:100213:1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3:100081:100</t>
-  </si>
-  <si>
-    <t xml:space="preserve">神铁</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3:100214:1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">陨铁精华</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3:700006:1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3:100078:1500#3:100079:1500</t>
-  </si>
-  <si>
-    <t xml:space="preserve">后羿皮肤</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3:700007:1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3:100080:1500#3:100081:1500</t>
-  </si>
-  <si>
-    <t xml:space="preserve">嫦娥皮肤</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3:900023:1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3:100078:1000#3:100079:1000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">春华秋实</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3:900024:1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3:100080:1000#3:100081:1000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">五谷丰登</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3:100093:300</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3:100093:400</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3:100093:700</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3:100094:30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3:100094:150</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3:100094:20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3:100095:200</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3:100095:40</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3:100095:10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3:800022:1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3:100093:700#3:100094:700#3:100095:700</t>
-  </si>
-  <si>
-    <t xml:space="preserve">头像框</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3:700012:1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3:100093:1000#3:100094:1000#3:100095:1000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">黄泉皮肤</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3:100099:10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3:100099:15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3:100099:1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3:100099:150</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3:100099:20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3:100099:100</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3:100099:5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3:100099:500</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3:100099:600</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3:100099:800</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3:100238:200</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3:100238:250</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3:100238:500</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3:100239:1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3:100239:15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3:100240:100</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3:100240:10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3:100240:50</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3:100240:5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3:100241:10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3:100241:100</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3:700010:1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3:100238:1500#3:100239:1500</t>
-  </si>
-  <si>
-    <t xml:space="preserve">鲲皮肤</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3:700016:1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3:100240:1500#3:100241:1500</t>
-  </si>
-  <si>
-    <t xml:space="preserve">夜魅皮肤</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3:100238:1000#3:100239:1000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3:100240:1000#3:100241:1000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3:100246:200</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3:100246:250</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3:100246:500</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3:100247:1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3:100247:15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3:100248:100</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3:100248:10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3:100248:50</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3:100248:5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3:100249:10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3:100249:100</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3:700018:1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3:100246:1500#3:100247:1500</t>
-  </si>
-  <si>
-    <t xml:space="preserve">醒狮</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3:700009:1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3:100248:1500#3:100249:1500</t>
-  </si>
-  <si>
-    <t xml:space="preserve">几何数论</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3:800033:1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3:100246:1000#3:100247:1000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">玫瑰芬芳</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4:608003:50</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3:100099:6500</t>
-  </si>
-  <si>
-    <t xml:space="preserve">光*1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4:602026:50</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3:100099:5000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">土地*50</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4:604019:50</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3:100099:4500</t>
-  </si>
-  <si>
-    <t xml:space="preserve">西王母*50</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4:604010:50</t>
-  </si>
-  <si>
-    <t xml:space="preserve">玉帝*50</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4:605008:50</t>
-  </si>
-  <si>
-    <t xml:space="preserve">刑天*50</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4:605013:50</t>
-  </si>
-  <si>
-    <t xml:space="preserve">烛龙*50</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4:602023:50</t>
-  </si>
-  <si>
-    <t xml:space="preserve">九天玄女*50</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4:601020:50</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3:100099:3000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">哪吒*50</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4:603022:50</t>
-  </si>
-  <si>
-    <t xml:space="preserve">妲己*50</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4:602018:50</t>
-  </si>
-  <si>
-    <t xml:space="preserve">斗战胜佛*50</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4:603024:50</t>
-  </si>
-  <si>
-    <t xml:space="preserve">曼珠*50</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4:602024:50</t>
-  </si>
-  <si>
-    <t xml:space="preserve">玄奘*50</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4:601017:50</t>
-  </si>
-  <si>
-    <t xml:space="preserve">后羿*50</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3:100099:1000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5星神族碎片*50</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5星魔族碎片*50</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3:100099:400</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7:55000101:1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">信仰*1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3:500026:1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">专属仙器自选*1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3:580001:1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">兽灵自选礼包*1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3:500014:1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">天级兽魂自选*1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3:100228:1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3:100099:4000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">生肖令*1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5:20001:5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3:100099:3500</t>
-  </si>
-  <si>
-    <t xml:space="preserve">龙魂*5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6:30002:2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">兽魂经验(大)*2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3:1200016:1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">雪花标志</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3:500011:1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">篆印自选礼包*1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0:0:100000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">金币*100000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0:4:50000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">英雄经验*50000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3:100099:300</t>
-  </si>
-  <si>
-    <t xml:space="preserve">高级寻宝券*1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">命签*1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3:590001:1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3:100099:450</t>
-  </si>
-  <si>
-    <t xml:space="preserve">幼龙自选*1</t>
   </si>
   <si>
     <t xml:space="preserve">3:200101:10</t>
@@ -20416,7 +20422,7 @@
         <v>1</v>
       </c>
       <c r="H2" t="s">
-        <v>122</v>
+        <v>555</v>
       </c>
     </row>
     <row r="3">
@@ -20424,13 +20430,13 @@
         <v>10002</v>
       </c>
       <c r="B3" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="C3" t="n">
         <v>10</v>
       </c>
       <c r="D3" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="E3" t="n">
         <v>1</v>
@@ -20440,7 +20446,7 @@
         <v>1</v>
       </c>
       <c r="H3" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
     </row>
     <row r="4">
@@ -20448,13 +20454,13 @@
         <v>10003</v>
       </c>
       <c r="B4" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="C4" t="n">
         <v>10</v>
       </c>
       <c r="D4" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="E4" t="n">
         <v>1</v>
@@ -20464,7 +20470,7 @@
         <v>1</v>
       </c>
       <c r="H4" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
     </row>
     <row r="5">
@@ -20472,13 +20478,13 @@
         <v>10004</v>
       </c>
       <c r="B5" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="C5" t="n">
         <v>10</v>
       </c>
       <c r="D5" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="E5" t="n">
         <v>1</v>
@@ -20488,7 +20494,7 @@
         <v>1</v>
       </c>
       <c r="H5" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
     </row>
     <row r="6">
@@ -20496,13 +20502,13 @@
         <v>10005</v>
       </c>
       <c r="B6" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="C6" t="n">
         <v>10</v>
       </c>
       <c r="D6" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="E6" t="n">
         <v>1</v>
@@ -20512,7 +20518,7 @@
         <v>1</v>
       </c>
       <c r="H6" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
     </row>
     <row r="7">
@@ -20520,13 +20526,13 @@
         <v>10006</v>
       </c>
       <c r="B7" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="C7" t="n">
         <v>10</v>
       </c>
       <c r="D7" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="E7" t="n">
         <v>1</v>
@@ -20536,7 +20542,7 @@
         <v>1</v>
       </c>
       <c r="H7" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
     </row>
     <row r="8">
@@ -20544,13 +20550,13 @@
         <v>11001</v>
       </c>
       <c r="B8" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="C8" t="n">
         <v>99</v>
       </c>
       <c r="D8" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="E8" t="n">
         <v>1</v>
@@ -20560,7 +20566,7 @@
         <v>2</v>
       </c>
       <c r="H8" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
     </row>
     <row r="9">
@@ -20568,13 +20574,13 @@
         <v>11002</v>
       </c>
       <c r="B9" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="C9" t="n">
         <v>99</v>
       </c>
       <c r="D9" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="E9" t="n">
         <v>1</v>
@@ -20584,7 +20590,7 @@
         <v>2</v>
       </c>
       <c r="H9" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
     </row>
     <row r="10">
@@ -20592,13 +20598,13 @@
         <v>11003</v>
       </c>
       <c r="B10" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="C10" t="n">
         <v>199</v>
       </c>
       <c r="D10" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="E10" t="n">
         <v>1</v>
@@ -20608,7 +20614,7 @@
         <v>2</v>
       </c>
       <c r="H10" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
     </row>
     <row r="11">
@@ -20616,13 +20622,13 @@
         <v>11004</v>
       </c>
       <c r="B11" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="C11" t="n">
         <v>199</v>
       </c>
       <c r="D11" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="E11" t="n">
         <v>1</v>
@@ -20632,7 +20638,7 @@
         <v>2</v>
       </c>
       <c r="H11" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
     </row>
     <row r="12">
@@ -20640,13 +20646,13 @@
         <v>12001</v>
       </c>
       <c r="B12" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="C12" t="n">
         <v>10</v>
       </c>
       <c r="D12" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="E12" t="n">
         <v>1</v>
@@ -20656,7 +20662,7 @@
         <v>3</v>
       </c>
       <c r="H12" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
     </row>
     <row r="13">
@@ -20664,13 +20670,13 @@
         <v>12002</v>
       </c>
       <c r="B13" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="C13" t="n">
         <v>10</v>
       </c>
       <c r="D13" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="E13" t="n">
         <v>1</v>
@@ -20680,7 +20686,7 @@
         <v>3</v>
       </c>
       <c r="H13" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
     </row>
     <row r="14">
@@ -20688,13 +20694,13 @@
         <v>12003</v>
       </c>
       <c r="B14" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="C14" t="n">
         <v>10</v>
       </c>
       <c r="D14" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="E14" t="n">
         <v>1</v>
@@ -20704,7 +20710,7 @@
         <v>3</v>
       </c>
       <c r="H14" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
     </row>
     <row r="15">
@@ -20712,13 +20718,13 @@
         <v>12004</v>
       </c>
       <c r="B15" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="C15" t="n">
         <v>99</v>
       </c>
       <c r="D15" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="E15" t="n">
         <v>1</v>
@@ -20728,7 +20734,7 @@
         <v>3</v>
       </c>
       <c r="H15" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
     </row>
     <row r="16">
@@ -20736,13 +20742,13 @@
         <v>13001</v>
       </c>
       <c r="B16" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="C16" t="n">
         <v>199</v>
       </c>
       <c r="D16" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="E16" t="n">
         <v>1</v>
@@ -20752,7 +20758,7 @@
         <v>4</v>
       </c>
       <c r="H16" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
     </row>
     <row r="17">
@@ -20760,13 +20766,13 @@
         <v>13002</v>
       </c>
       <c r="B17" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="C17" t="n">
         <v>199</v>
       </c>
       <c r="D17" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="E17" t="n">
         <v>1</v>
@@ -20776,7 +20782,7 @@
         <v>4</v>
       </c>
       <c r="H17" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
     </row>
     <row r="18">
@@ -20784,13 +20790,13 @@
         <v>13003</v>
       </c>
       <c r="B18" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="C18" t="n">
         <v>199</v>
       </c>
       <c r="D18" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="E18" t="n">
         <v>1</v>
@@ -20800,7 +20806,7 @@
         <v>4</v>
       </c>
       <c r="H18" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
     </row>
     <row r="19">
@@ -20808,13 +20814,13 @@
         <v>14001</v>
       </c>
       <c r="B19" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="C19" t="n">
         <v>1</v>
       </c>
       <c r="D19" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="E19" t="n">
         <v>1</v>
@@ -20823,7 +20829,7 @@
         <v>5</v>
       </c>
       <c r="H19" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
     </row>
     <row r="20">
@@ -20831,13 +20837,13 @@
         <v>14002</v>
       </c>
       <c r="B20" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="C20" t="n">
         <v>1</v>
       </c>
       <c r="D20" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="E20" t="n">
         <v>1</v>
@@ -20846,7 +20852,7 @@
         <v>5</v>
       </c>
       <c r="H20" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
     </row>
     <row r="21">
@@ -20854,13 +20860,13 @@
         <v>14003</v>
       </c>
       <c r="B21" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="C21" t="n">
         <v>1</v>
       </c>
       <c r="D21" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="E21" t="n">
         <v>1</v>
@@ -20869,7 +20875,7 @@
         <v>5</v>
       </c>
       <c r="H21" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
     </row>
     <row r="22">
@@ -20877,13 +20883,13 @@
         <v>14004</v>
       </c>
       <c r="B22" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="C22" t="n">
         <v>1</v>
       </c>
       <c r="D22" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="E22" t="n">
         <v>1</v>
@@ -20892,7 +20898,7 @@
         <v>5</v>
       </c>
       <c r="H22" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
     </row>
     <row r="23">
@@ -20906,7 +20912,7 @@
         <v>10</v>
       </c>
       <c r="D23" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="E23" t="n">
         <v>2</v>
@@ -20916,7 +20922,7 @@
         <v>1</v>
       </c>
       <c r="H23" t="s">
-        <v>122</v>
+        <v>555</v>
       </c>
     </row>
     <row r="24">
@@ -20924,13 +20930,13 @@
         <v>20002</v>
       </c>
       <c r="B24" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="C24" t="n">
         <v>5</v>
       </c>
       <c r="D24" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="E24" t="n">
         <v>2</v>
@@ -20940,7 +20946,7 @@
         <v>1</v>
       </c>
       <c r="H24" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
     </row>
     <row r="25">
@@ -20948,13 +20954,13 @@
         <v>20003</v>
       </c>
       <c r="B25" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="C25" t="n">
         <v>5</v>
       </c>
       <c r="D25" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="E25" t="n">
         <v>2</v>
@@ -20964,7 +20970,7 @@
         <v>1</v>
       </c>
       <c r="H25" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
     </row>
     <row r="26">
@@ -20972,13 +20978,13 @@
         <v>20004</v>
       </c>
       <c r="B26" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="C26" t="n">
         <v>5</v>
       </c>
       <c r="D26" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="E26" t="n">
         <v>2</v>
@@ -20988,7 +20994,7 @@
         <v>1</v>
       </c>
       <c r="H26" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
     </row>
     <row r="27">
@@ -20996,13 +21002,13 @@
         <v>20005</v>
       </c>
       <c r="B27" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="C27" t="n">
         <v>5</v>
       </c>
       <c r="D27" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="E27" t="n">
         <v>2</v>
@@ -21012,7 +21018,7 @@
         <v>1</v>
       </c>
       <c r="H27" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
     </row>
     <row r="28">
@@ -21020,13 +21026,13 @@
         <v>20006</v>
       </c>
       <c r="B28" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="C28" t="n">
         <v>5</v>
       </c>
       <c r="D28" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="E28" t="n">
         <v>2</v>
@@ -21036,7 +21042,7 @@
         <v>1</v>
       </c>
       <c r="H28" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
     </row>
     <row r="29">
@@ -21044,13 +21050,13 @@
         <v>21001</v>
       </c>
       <c r="B29" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="C29" t="n">
         <v>100</v>
       </c>
       <c r="D29" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="E29" t="n">
         <v>2</v>
@@ -21060,7 +21066,7 @@
         <v>2</v>
       </c>
       <c r="H29" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
     </row>
     <row r="30">
@@ -21074,7 +21080,7 @@
         <v>10</v>
       </c>
       <c r="D30" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="E30" t="n">
         <v>2</v>
@@ -21092,13 +21098,13 @@
         <v>21003</v>
       </c>
       <c r="B31" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="C31" t="n">
         <v>100</v>
       </c>
       <c r="D31" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="E31" t="n">
         <v>2</v>
@@ -21108,7 +21114,7 @@
         <v>2</v>
       </c>
       <c r="H31" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
     </row>
     <row r="32">
@@ -21116,13 +21122,13 @@
         <v>21004</v>
       </c>
       <c r="B32" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="C32" t="n">
         <v>100</v>
       </c>
       <c r="D32" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="E32" t="n">
         <v>2</v>
@@ -21132,7 +21138,7 @@
         <v>2</v>
       </c>
       <c r="H32" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
     </row>
     <row r="33">
@@ -21140,13 +21146,13 @@
         <v>21005</v>
       </c>
       <c r="B33" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="C33" t="n">
         <v>100</v>
       </c>
       <c r="D33" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="E33" t="n">
         <v>2</v>
@@ -21156,7 +21162,7 @@
         <v>2</v>
       </c>
       <c r="H33" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
     </row>
     <row r="34">
@@ -21164,13 +21170,13 @@
         <v>22001</v>
       </c>
       <c r="B34" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="C34" t="n">
         <v>10</v>
       </c>
       <c r="D34" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="E34" t="n">
         <v>2</v>
@@ -21180,7 +21186,7 @@
         <v>3</v>
       </c>
       <c r="H34" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
     </row>
     <row r="35">
@@ -21188,13 +21194,13 @@
         <v>22002</v>
       </c>
       <c r="B35" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="C35" t="n">
         <v>10</v>
       </c>
       <c r="D35" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="E35" t="n">
         <v>2</v>
@@ -21204,7 +21210,7 @@
         <v>3</v>
       </c>
       <c r="H35" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
     </row>
     <row r="36">
@@ -21212,13 +21218,13 @@
         <v>22003</v>
       </c>
       <c r="B36" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="C36" t="n">
         <v>10</v>
       </c>
       <c r="D36" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="E36" t="n">
         <v>2</v>
@@ -21228,7 +21234,7 @@
         <v>3</v>
       </c>
       <c r="H36" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
     </row>
     <row r="37">
@@ -21236,13 +21242,13 @@
         <v>22004</v>
       </c>
       <c r="B37" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="C37" t="n">
         <v>100</v>
       </c>
       <c r="D37" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="E37" t="n">
         <v>2</v>
@@ -21252,7 +21258,7 @@
         <v>3</v>
       </c>
       <c r="H37" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
     </row>
     <row r="38">
@@ -21260,13 +21266,13 @@
         <v>23001</v>
       </c>
       <c r="B38" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="C38" t="n">
         <v>1</v>
       </c>
       <c r="D38" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="E38" t="n">
         <v>2</v>
@@ -21276,7 +21282,7 @@
         <v>4</v>
       </c>
       <c r="H38" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
     </row>
     <row r="39">
@@ -21284,13 +21290,13 @@
         <v>23002</v>
       </c>
       <c r="B39" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="C39" t="n">
         <v>1</v>
       </c>
       <c r="D39" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="E39" t="n">
         <v>2</v>
@@ -21300,7 +21306,7 @@
         <v>4</v>
       </c>
       <c r="H39" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
     </row>
     <row r="40">
@@ -21308,13 +21314,13 @@
         <v>30001</v>
       </c>
       <c r="B40" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="C40" t="n">
         <v>99</v>
       </c>
       <c r="D40" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="E40" t="n">
         <v>3</v>
@@ -21324,7 +21330,7 @@
         <v>1</v>
       </c>
       <c r="H40" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
     </row>
     <row r="41">
@@ -21332,13 +21338,13 @@
         <v>30002</v>
       </c>
       <c r="B41" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="C41" t="n">
         <v>99</v>
       </c>
       <c r="D41" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="E41" t="n">
         <v>3</v>
@@ -21348,7 +21354,7 @@
         <v>1</v>
       </c>
       <c r="H41" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
     </row>
     <row r="42">
@@ -21356,13 +21362,13 @@
         <v>30003</v>
       </c>
       <c r="B42" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="C42" t="n">
         <v>199</v>
       </c>
       <c r="D42" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="E42" t="n">
         <v>3</v>
@@ -21372,7 +21378,7 @@
         <v>1</v>
       </c>
       <c r="H42" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
     </row>
     <row r="43">
@@ -21380,13 +21386,13 @@
         <v>30004</v>
       </c>
       <c r="B43" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="C43" t="n">
         <v>199</v>
       </c>
       <c r="D43" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="E43" t="n">
         <v>3</v>
@@ -21396,7 +21402,7 @@
         <v>1</v>
       </c>
       <c r="H43" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
     </row>
     <row r="44">
@@ -21404,13 +21410,13 @@
         <v>30005</v>
       </c>
       <c r="B44" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="C44" t="n">
         <v>10</v>
       </c>
       <c r="D44" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="E44" t="n">
         <v>3</v>
@@ -21420,7 +21426,7 @@
         <v>1</v>
       </c>
       <c r="H44" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
     </row>
     <row r="45">
@@ -21428,13 +21434,13 @@
         <v>30006</v>
       </c>
       <c r="B45" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="C45" t="n">
         <v>10</v>
       </c>
       <c r="D45" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="E45" t="n">
         <v>3</v>
@@ -21444,7 +21450,7 @@
         <v>1</v>
       </c>
       <c r="H45" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
     </row>
     <row r="46">
@@ -21452,13 +21458,13 @@
         <v>30007</v>
       </c>
       <c r="B46" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="C46" t="n">
         <v>10</v>
       </c>
       <c r="D46" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="E46" t="n">
         <v>3</v>
@@ -21468,7 +21474,7 @@
         <v>1</v>
       </c>
       <c r="H46" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
     </row>
     <row r="47">
@@ -21476,13 +21482,13 @@
         <v>30008</v>
       </c>
       <c r="B47" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="C47" t="n">
         <v>99</v>
       </c>
       <c r="D47" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="E47" t="n">
         <v>3</v>
@@ -21492,7 +21498,7 @@
         <v>1</v>
       </c>
       <c r="H47" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
     </row>
     <row r="48">
@@ -21506,7 +21512,7 @@
         <v>10</v>
       </c>
       <c r="D48" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="E48" t="n">
         <v>3</v>
@@ -21516,7 +21522,7 @@
         <v>2</v>
       </c>
       <c r="H48" t="s">
-        <v>122</v>
+        <v>555</v>
       </c>
     </row>
     <row r="49">
@@ -21524,13 +21530,13 @@
         <v>31002</v>
       </c>
       <c r="B49" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="C49" t="n">
         <v>5</v>
       </c>
       <c r="D49" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="E49" t="n">
         <v>3</v>
@@ -21540,7 +21546,7 @@
         <v>2</v>
       </c>
       <c r="H49" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
     </row>
     <row r="50">
@@ -21548,13 +21554,13 @@
         <v>31003</v>
       </c>
       <c r="B50" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="C50" t="n">
         <v>5</v>
       </c>
       <c r="D50" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="E50" t="n">
         <v>3</v>
@@ -21564,7 +21570,7 @@
         <v>2</v>
       </c>
       <c r="H50" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
     </row>
     <row r="51">
@@ -21572,13 +21578,13 @@
         <v>31004</v>
       </c>
       <c r="B51" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="C51" t="n">
         <v>5</v>
       </c>
       <c r="D51" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="E51" t="n">
         <v>3</v>
@@ -21588,7 +21594,7 @@
         <v>2</v>
       </c>
       <c r="H51" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
     </row>
     <row r="52">
@@ -21596,13 +21602,13 @@
         <v>31005</v>
       </c>
       <c r="B52" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="C52" t="n">
         <v>5</v>
       </c>
       <c r="D52" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="E52" t="n">
         <v>3</v>
@@ -21612,7 +21618,7 @@
         <v>2</v>
       </c>
       <c r="H52" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
     </row>
     <row r="53">
@@ -21620,13 +21626,13 @@
         <v>31006</v>
       </c>
       <c r="B53" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="C53" t="n">
         <v>5</v>
       </c>
       <c r="D53" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="E53" t="n">
         <v>3</v>
@@ -21636,7 +21642,7 @@
         <v>2</v>
       </c>
       <c r="H53" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
     </row>
     <row r="54">
@@ -21650,7 +21656,7 @@
         <v>10</v>
       </c>
       <c r="D54" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="E54" t="n">
         <v>4</v>
@@ -21660,7 +21666,7 @@
         <v>1</v>
       </c>
       <c r="H54" t="s">
-        <v>122</v>
+        <v>555</v>
       </c>
     </row>
     <row r="55">
@@ -21668,13 +21674,13 @@
         <v>40002</v>
       </c>
       <c r="B55" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="C55" t="n">
         <v>10</v>
       </c>
       <c r="D55" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="E55" t="n">
         <v>4</v>
@@ -21684,7 +21690,7 @@
         <v>1</v>
       </c>
       <c r="H55" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
     </row>
     <row r="56">
@@ -21692,13 +21698,13 @@
         <v>40003</v>
       </c>
       <c r="B56" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="C56" t="n">
         <v>10</v>
       </c>
       <c r="D56" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="E56" t="n">
         <v>4</v>
@@ -21708,7 +21714,7 @@
         <v>1</v>
       </c>
       <c r="H56" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
     </row>
     <row r="57">
@@ -21716,13 +21722,13 @@
         <v>40004</v>
       </c>
       <c r="B57" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="C57" t="n">
         <v>10</v>
       </c>
       <c r="D57" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="E57" t="n">
         <v>4</v>
@@ -21732,7 +21738,7 @@
         <v>1</v>
       </c>
       <c r="H57" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
     </row>
     <row r="58">
@@ -21740,13 +21746,13 @@
         <v>40005</v>
       </c>
       <c r="B58" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="C58" t="n">
         <v>10</v>
       </c>
       <c r="D58" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="E58" t="n">
         <v>4</v>
@@ -21756,7 +21762,7 @@
         <v>1</v>
       </c>
       <c r="H58" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
     </row>
     <row r="59">
@@ -21764,13 +21770,13 @@
         <v>40006</v>
       </c>
       <c r="B59" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="C59" t="n">
         <v>10</v>
       </c>
       <c r="D59" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="E59" t="n">
         <v>4</v>
@@ -21780,7 +21786,7 @@
         <v>1</v>
       </c>
       <c r="H59" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
     </row>
     <row r="60">
@@ -21788,13 +21794,13 @@
         <v>41001</v>
       </c>
       <c r="B60" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="C60" t="n">
         <v>99</v>
       </c>
       <c r="D60" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="E60" t="n">
         <v>4</v>
@@ -21804,7 +21810,7 @@
         <v>2</v>
       </c>
       <c r="H60" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
     </row>
     <row r="61">
@@ -21812,13 +21818,13 @@
         <v>41002</v>
       </c>
       <c r="B61" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="C61" t="n">
         <v>99</v>
       </c>
       <c r="D61" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="E61" t="n">
         <v>4</v>
@@ -21828,7 +21834,7 @@
         <v>2</v>
       </c>
       <c r="H61" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
     </row>
     <row r="62">
@@ -21836,13 +21842,13 @@
         <v>41003</v>
       </c>
       <c r="B62" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="C62" t="n">
         <v>199</v>
       </c>
       <c r="D62" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="E62" t="n">
         <v>4</v>
@@ -21852,7 +21858,7 @@
         <v>2</v>
       </c>
       <c r="H62" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
     </row>
     <row r="63">
@@ -21860,13 +21866,13 @@
         <v>41004</v>
       </c>
       <c r="B63" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="C63" t="n">
         <v>199</v>
       </c>
       <c r="D63" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="E63" t="n">
         <v>4</v>
@@ -21876,7 +21882,7 @@
         <v>2</v>
       </c>
       <c r="H63" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
     </row>
     <row r="64">
@@ -21884,13 +21890,13 @@
         <v>42001</v>
       </c>
       <c r="B64" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="C64" t="n">
         <v>10</v>
       </c>
       <c r="D64" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="E64" t="n">
         <v>4</v>
@@ -21900,7 +21906,7 @@
         <v>3</v>
       </c>
       <c r="H64" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
     </row>
     <row r="65">
@@ -21908,13 +21914,13 @@
         <v>42002</v>
       </c>
       <c r="B65" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="C65" t="n">
         <v>10</v>
       </c>
       <c r="D65" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="E65" t="n">
         <v>4</v>
@@ -21924,7 +21930,7 @@
         <v>3</v>
       </c>
       <c r="H65" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
     </row>
     <row r="66">
@@ -21932,13 +21938,13 @@
         <v>42003</v>
       </c>
       <c r="B66" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="C66" t="n">
         <v>10</v>
       </c>
       <c r="D66" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="E66" t="n">
         <v>4</v>
@@ -21948,7 +21954,7 @@
         <v>3</v>
       </c>
       <c r="H66" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
     </row>
     <row r="67">
@@ -21956,13 +21962,13 @@
         <v>42004</v>
       </c>
       <c r="B67" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="C67" t="n">
         <v>99</v>
       </c>
       <c r="D67" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="E67" t="n">
         <v>4</v>
@@ -21972,7 +21978,7 @@
         <v>3</v>
       </c>
       <c r="H67" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
     </row>
     <row r="68">
@@ -21980,13 +21986,13 @@
         <v>43001</v>
       </c>
       <c r="B68" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="C68" t="n">
         <v>199</v>
       </c>
       <c r="D68" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="E68" t="n">
         <v>4</v>
@@ -21996,7 +22002,7 @@
         <v>4</v>
       </c>
       <c r="H68" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
     </row>
     <row r="69">
@@ -22004,13 +22010,13 @@
         <v>43002</v>
       </c>
       <c r="B69" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="C69" t="n">
         <v>199</v>
       </c>
       <c r="D69" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="E69" t="n">
         <v>4</v>
@@ -22020,7 +22026,7 @@
         <v>4</v>
       </c>
       <c r="H69" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
     </row>
     <row r="70">
@@ -22028,13 +22034,13 @@
         <v>43003</v>
       </c>
       <c r="B70" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="C70" t="n">
         <v>199</v>
       </c>
       <c r="D70" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="E70" t="n">
         <v>4</v>
@@ -22044,7 +22050,7 @@
         <v>4</v>
       </c>
       <c r="H70" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
     </row>
     <row r="71">
@@ -22052,13 +22058,13 @@
         <v>44001</v>
       </c>
       <c r="B71" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="C71" t="n">
         <v>1</v>
       </c>
       <c r="D71" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="E71" t="n">
         <v>4</v>
@@ -22067,7 +22073,7 @@
         <v>5</v>
       </c>
       <c r="H71" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
     </row>
     <row r="72">
@@ -22075,13 +22081,13 @@
         <v>44002</v>
       </c>
       <c r="B72" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="C72" t="n">
         <v>1</v>
       </c>
       <c r="D72" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="E72" t="n">
         <v>4</v>
@@ -22090,7 +22096,7 @@
         <v>5</v>
       </c>
       <c r="H72" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
     </row>
     <row r="73">
@@ -22098,13 +22104,13 @@
         <v>44003</v>
       </c>
       <c r="B73" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="C73" t="n">
         <v>1</v>
       </c>
       <c r="D73" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="E73" t="n">
         <v>4</v>
@@ -22113,7 +22119,7 @@
         <v>5</v>
       </c>
       <c r="H73" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
     </row>
     <row r="74">
@@ -22121,13 +22127,13 @@
         <v>44004</v>
       </c>
       <c r="B74" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="C74" t="n">
         <v>1</v>
       </c>
       <c r="D74" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="E74" t="n">
         <v>4</v>
@@ -22136,7 +22142,7 @@
         <v>5</v>
       </c>
       <c r="H74" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
     </row>
     <row r="75">
@@ -22150,7 +22156,7 @@
         <v>10</v>
       </c>
       <c r="D75" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="E75" t="n">
         <v>5</v>
@@ -22159,7 +22165,7 @@
         <v>1</v>
       </c>
       <c r="H75" t="s">
-        <v>122</v>
+        <v>555</v>
       </c>
     </row>
     <row r="76">
@@ -22167,13 +22173,13 @@
         <v>50002</v>
       </c>
       <c r="B76" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="C76" t="n">
         <v>10</v>
       </c>
       <c r="D76" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="E76" t="n">
         <v>5</v>
@@ -22183,7 +22189,7 @@
         <v>1</v>
       </c>
       <c r="H76" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
     </row>
     <row r="77">
@@ -22191,13 +22197,13 @@
         <v>50003</v>
       </c>
       <c r="B77" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="C77" t="n">
         <v>10</v>
       </c>
       <c r="D77" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="E77" t="n">
         <v>5</v>
@@ -22207,7 +22213,7 @@
         <v>1</v>
       </c>
       <c r="H77" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
     </row>
     <row r="78">
@@ -22215,13 +22221,13 @@
         <v>50004</v>
       </c>
       <c r="B78" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="C78" t="n">
         <v>10</v>
       </c>
       <c r="D78" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="E78" t="n">
         <v>5</v>
@@ -22231,7 +22237,7 @@
         <v>1</v>
       </c>
       <c r="H78" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
     </row>
     <row r="79">
@@ -22239,13 +22245,13 @@
         <v>50005</v>
       </c>
       <c r="B79" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="C79" t="n">
         <v>10</v>
       </c>
       <c r="D79" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="E79" t="n">
         <v>5</v>
@@ -22255,7 +22261,7 @@
         <v>1</v>
       </c>
       <c r="H79" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
     </row>
     <row r="80">
@@ -22263,13 +22269,13 @@
         <v>50006</v>
       </c>
       <c r="B80" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="C80" t="n">
         <v>10</v>
       </c>
       <c r="D80" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="E80" t="n">
         <v>5</v>
@@ -22279,7 +22285,7 @@
         <v>1</v>
       </c>
       <c r="H80" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
     </row>
     <row r="81">
@@ -22287,13 +22293,13 @@
         <v>51001</v>
       </c>
       <c r="B81" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="C81" t="n">
         <v>99</v>
       </c>
       <c r="D81" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="E81" t="n">
         <v>5</v>
@@ -22303,7 +22309,7 @@
         <v>2</v>
       </c>
       <c r="H81" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
     </row>
     <row r="82">
@@ -22311,13 +22317,13 @@
         <v>51002</v>
       </c>
       <c r="B82" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="C82" t="n">
         <v>99</v>
       </c>
       <c r="D82" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="E82" t="n">
         <v>5</v>
@@ -22327,7 +22333,7 @@
         <v>2</v>
       </c>
       <c r="H82" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
     </row>
     <row r="83">
@@ -22335,13 +22341,13 @@
         <v>51003</v>
       </c>
       <c r="B83" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="C83" t="n">
         <v>199</v>
       </c>
       <c r="D83" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="E83" t="n">
         <v>5</v>
@@ -22351,7 +22357,7 @@
         <v>2</v>
       </c>
       <c r="H83" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
     </row>
     <row r="84">
@@ -22359,13 +22365,13 @@
         <v>51004</v>
       </c>
       <c r="B84" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="C84" t="n">
         <v>199</v>
       </c>
       <c r="D84" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="E84" t="n">
         <v>5</v>
@@ -22375,7 +22381,7 @@
         <v>2</v>
       </c>
       <c r="H84" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
     </row>
     <row r="85">
@@ -22383,13 +22389,13 @@
         <v>52001</v>
       </c>
       <c r="B85" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="C85" t="n">
         <v>10</v>
       </c>
       <c r="D85" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="E85" t="n">
         <v>5</v>
@@ -22399,7 +22405,7 @@
         <v>3</v>
       </c>
       <c r="H85" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
     </row>
     <row r="86">
@@ -22407,13 +22413,13 @@
         <v>52002</v>
       </c>
       <c r="B86" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="C86" t="n">
         <v>10</v>
       </c>
       <c r="D86" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="E86" t="n">
         <v>5</v>
@@ -22423,7 +22429,7 @@
         <v>3</v>
       </c>
       <c r="H86" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
     </row>
     <row r="87">
@@ -22431,13 +22437,13 @@
         <v>52003</v>
       </c>
       <c r="B87" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="C87" t="n">
         <v>10</v>
       </c>
       <c r="D87" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="E87" t="n">
         <v>5</v>
@@ -22447,7 +22453,7 @@
         <v>3</v>
       </c>
       <c r="H87" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
     </row>
     <row r="88">
@@ -22455,13 +22461,13 @@
         <v>52004</v>
       </c>
       <c r="B88" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="C88" t="n">
         <v>99</v>
       </c>
       <c r="D88" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="E88" t="n">
         <v>5</v>
@@ -22471,7 +22477,7 @@
         <v>3</v>
       </c>
       <c r="H88" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
     </row>
     <row r="89">
@@ -22479,13 +22485,13 @@
         <v>53001</v>
       </c>
       <c r="B89" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="C89" t="n">
         <v>199</v>
       </c>
       <c r="D89" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="E89" t="n">
         <v>5</v>
@@ -22495,7 +22501,7 @@
         <v>4</v>
       </c>
       <c r="H89" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
     </row>
     <row r="90">
@@ -22503,13 +22509,13 @@
         <v>53002</v>
       </c>
       <c r="B90" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="C90" t="n">
         <v>199</v>
       </c>
       <c r="D90" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="E90" t="n">
         <v>5</v>
@@ -22519,7 +22525,7 @@
         <v>4</v>
       </c>
       <c r="H90" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
     </row>
     <row r="91">
@@ -22527,13 +22533,13 @@
         <v>53003</v>
       </c>
       <c r="B91" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="C91" t="n">
         <v>199</v>
       </c>
       <c r="D91" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="E91" t="n">
         <v>5</v>
@@ -22543,7 +22549,7 @@
         <v>4</v>
       </c>
       <c r="H91" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
     </row>
     <row r="92">
@@ -22551,13 +22557,13 @@
         <v>54001</v>
       </c>
       <c r="B92" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="C92" t="n">
         <v>1</v>
       </c>
       <c r="D92" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="E92" t="n">
         <v>5</v>
@@ -22566,7 +22572,7 @@
         <v>1</v>
       </c>
       <c r="H92" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
     </row>
     <row r="93">
@@ -22574,13 +22580,13 @@
         <v>54002</v>
       </c>
       <c r="B93" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="C93" t="n">
         <v>1</v>
       </c>
       <c r="D93" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="E93" t="n">
         <v>5</v>
@@ -22589,7 +22595,7 @@
         <v>1</v>
       </c>
       <c r="H93" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
     </row>
     <row r="94">
@@ -22597,13 +22603,13 @@
         <v>54003</v>
       </c>
       <c r="B94" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="C94" t="n">
         <v>1</v>
       </c>
       <c r="D94" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="E94" t="n">
         <v>5</v>
@@ -22612,7 +22618,7 @@
         <v>1</v>
       </c>
       <c r="H94" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
     </row>
     <row r="95">
@@ -22620,13 +22626,13 @@
         <v>60001</v>
       </c>
       <c r="B95" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="C95" t="n">
         <v>19</v>
       </c>
       <c r="D95" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="E95" t="n">
         <v>6</v>
@@ -22635,7 +22641,7 @@
         <v>1</v>
       </c>
       <c r="H95" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="K95"/>
       <c r="L95"/>
@@ -22646,13 +22652,13 @@
         <v>60002</v>
       </c>
       <c r="B96" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="C96" t="n">
         <v>19</v>
       </c>
       <c r="D96" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="E96" t="n">
         <v>6</v>
@@ -22661,7 +22667,7 @@
         <v>1</v>
       </c>
       <c r="H96" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="K96"/>
       <c r="L96"/>
@@ -22672,13 +22678,13 @@
         <v>60003</v>
       </c>
       <c r="B97" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="C97" t="n">
         <v>19</v>
       </c>
       <c r="D97" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="E97" t="n">
         <v>6</v>
@@ -22687,7 +22693,7 @@
         <v>1</v>
       </c>
       <c r="H97" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="K97"/>
       <c r="L97"/>
@@ -22698,13 +22704,13 @@
         <v>60004</v>
       </c>
       <c r="B98" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="C98" t="n">
         <v>19</v>
       </c>
       <c r="D98" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="E98" t="n">
         <v>6</v>
@@ -22713,7 +22719,7 @@
         <v>1</v>
       </c>
       <c r="H98" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="K98"/>
       <c r="L98"/>
@@ -22724,13 +22730,13 @@
         <v>60005</v>
       </c>
       <c r="B99" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="C99" t="n">
         <v>19</v>
       </c>
       <c r="D99" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="E99" t="n">
         <v>6</v>
@@ -22739,7 +22745,7 @@
         <v>1</v>
       </c>
       <c r="H99" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="K99"/>
       <c r="L99"/>
@@ -22750,13 +22756,13 @@
         <v>60006</v>
       </c>
       <c r="B100" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="C100" t="n">
         <v>19</v>
       </c>
       <c r="D100" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="E100" t="n">
         <v>6</v>
@@ -22765,7 +22771,7 @@
         <v>1</v>
       </c>
       <c r="H100" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="K100"/>
       <c r="L100"/>
@@ -22776,13 +22782,13 @@
         <v>60007</v>
       </c>
       <c r="B101" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="C101" t="n">
         <v>19</v>
       </c>
       <c r="D101" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="E101" t="n">
         <v>6</v>
@@ -22791,7 +22797,7 @@
         <v>1</v>
       </c>
       <c r="H101" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="K101"/>
       <c r="L101"/>
@@ -22802,13 +22808,13 @@
         <v>60008</v>
       </c>
       <c r="B102" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="C102" t="n">
         <v>19</v>
       </c>
       <c r="D102" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="E102" t="n">
         <v>6</v>
@@ -22817,7 +22823,7 @@
         <v>1</v>
       </c>
       <c r="H102" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="K102"/>
       <c r="L102"/>
@@ -22828,13 +22834,13 @@
         <v>60009</v>
       </c>
       <c r="B103" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="C103" t="n">
         <v>19</v>
       </c>
       <c r="D103" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="E103" t="n">
         <v>6</v>
@@ -22843,7 +22849,7 @@
         <v>1</v>
       </c>
       <c r="H103" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="K103"/>
       <c r="L103"/>
@@ -22854,13 +22860,13 @@
         <v>60010</v>
       </c>
       <c r="B104" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="C104" t="n">
         <v>19</v>
       </c>
       <c r="D104" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="E104" t="n">
         <v>6</v>
@@ -22869,7 +22875,7 @@
         <v>1</v>
       </c>
       <c r="H104" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="K104"/>
       <c r="L104"/>
@@ -22880,13 +22886,13 @@
         <v>60011</v>
       </c>
       <c r="B105" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="C105" t="n">
         <v>19</v>
       </c>
       <c r="D105" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="E105" t="n">
         <v>6</v>
@@ -22895,7 +22901,7 @@
         <v>1</v>
       </c>
       <c r="H105" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="K105"/>
       <c r="L105"/>
@@ -22906,13 +22912,13 @@
         <v>60012</v>
       </c>
       <c r="B106" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="C106" t="n">
         <v>19</v>
       </c>
       <c r="D106" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="E106" t="n">
         <v>6</v>
@@ -22921,7 +22927,7 @@
         <v>1</v>
       </c>
       <c r="H106" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="K106"/>
       <c r="L106"/>
@@ -22932,13 +22938,13 @@
         <v>60013</v>
       </c>
       <c r="B107" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="C107" t="n">
         <v>19</v>
       </c>
       <c r="D107" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="E107" t="n">
         <v>6</v>
@@ -22947,7 +22953,7 @@
         <v>1</v>
       </c>
       <c r="H107" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="K107"/>
       <c r="L107"/>
@@ -22958,13 +22964,13 @@
         <v>60014</v>
       </c>
       <c r="B108" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="C108" t="n">
         <v>30</v>
       </c>
       <c r="D108" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="E108" t="n">
         <v>6</v>
@@ -22973,7 +22979,7 @@
         <v>1</v>
       </c>
       <c r="H108" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="K108"/>
       <c r="L108"/>
@@ -22984,13 +22990,13 @@
         <v>60015</v>
       </c>
       <c r="B109" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="C109" t="n">
         <v>30</v>
       </c>
       <c r="D109" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="E109" t="n">
         <v>6</v>
@@ -22999,7 +23005,7 @@
         <v>1</v>
       </c>
       <c r="H109" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="K109"/>
       <c r="L109"/>
@@ -23016,7 +23022,7 @@
         <v>30</v>
       </c>
       <c r="D110" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="E110" t="n">
         <v>6</v>
@@ -23025,7 +23031,7 @@
         <v>1</v>
       </c>
       <c r="H110" t="s">
-        <v>122</v>
+        <v>555</v>
       </c>
       <c r="K110"/>
       <c r="L110"/>
@@ -23036,13 +23042,13 @@
         <v>60017</v>
       </c>
       <c r="B111" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="C111" t="n">
         <v>7</v>
       </c>
       <c r="D111" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="E111" t="n">
         <v>6</v>
@@ -23051,7 +23057,7 @@
         <v>2</v>
       </c>
       <c r="H111" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="K111"/>
       <c r="L111"/>
@@ -23062,13 +23068,13 @@
         <v>60018</v>
       </c>
       <c r="B112" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="C112" t="n">
         <v>14</v>
       </c>
       <c r="D112" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="E112" t="n">
         <v>6</v>
@@ -23077,7 +23083,7 @@
         <v>2</v>
       </c>
       <c r="H112" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="K112"/>
       <c r="L112"/>
@@ -23088,13 +23094,13 @@
         <v>60019</v>
       </c>
       <c r="B113" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="C113" t="n">
         <v>1</v>
       </c>
       <c r="D113" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="E113" t="n">
         <v>6</v>
@@ -23103,7 +23109,7 @@
         <v>2</v>
       </c>
       <c r="H113" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="K113"/>
       <c r="L113"/>
@@ -23114,13 +23120,13 @@
         <v>60020</v>
       </c>
       <c r="B114" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="C114" t="n">
         <v>5</v>
       </c>
       <c r="D114" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="E114" t="n">
         <v>6</v>
@@ -23129,7 +23135,7 @@
         <v>2</v>
       </c>
       <c r="H114" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="K114"/>
       <c r="L114"/>
@@ -23140,13 +23146,13 @@
         <v>60021</v>
       </c>
       <c r="B115" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="C115" t="n">
         <v>5</v>
       </c>
       <c r="D115" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="E115" t="n">
         <v>6</v>
@@ -23155,7 +23161,7 @@
         <v>2</v>
       </c>
       <c r="H115" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="K115"/>
       <c r="L115"/>
@@ -23166,13 +23172,13 @@
         <v>60022</v>
       </c>
       <c r="B116" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="C116" t="n">
         <v>5</v>
       </c>
       <c r="D116" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E116" t="n">
         <v>6</v>
@@ -23181,7 +23187,7 @@
         <v>2</v>
       </c>
       <c r="H116" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="K116"/>
       <c r="L116"/>
@@ -23192,13 +23198,13 @@
         <v>60023</v>
       </c>
       <c r="B117" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="C117" t="n">
         <v>40</v>
       </c>
       <c r="D117" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="E117" t="n">
         <v>6</v>
@@ -23207,7 +23213,7 @@
         <v>2</v>
       </c>
       <c r="H117" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="K117"/>
       <c r="L117"/>
@@ -23218,13 +23224,13 @@
         <v>60024</v>
       </c>
       <c r="B118" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="C118" t="n">
         <v>1</v>
       </c>
       <c r="D118" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="E118" t="n">
         <v>6</v>
@@ -23233,7 +23239,7 @@
         <v>2</v>
       </c>
       <c r="H118" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="K118"/>
       <c r="L118"/>
@@ -23244,13 +23250,13 @@
         <v>60025</v>
       </c>
       <c r="B119" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="C119" t="n">
         <v>15</v>
       </c>
       <c r="D119" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="E119" t="n">
         <v>6</v>
@@ -23259,7 +23265,7 @@
         <v>2</v>
       </c>
       <c r="H119" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="K119"/>
       <c r="L119"/>
@@ -23270,13 +23276,13 @@
         <v>60026</v>
       </c>
       <c r="B120" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="C120" t="n">
         <v>299</v>
       </c>
       <c r="D120" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="E120" t="n">
         <v>6</v>
@@ -23285,7 +23291,7 @@
         <v>3</v>
       </c>
       <c r="H120" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="L120"/>
     </row>
@@ -23294,13 +23300,13 @@
         <v>60027</v>
       </c>
       <c r="B121" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="C121" t="n">
         <v>199</v>
       </c>
       <c r="D121" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="E121" t="n">
         <v>6</v>
@@ -23310,7 +23316,7 @@
         <v>3</v>
       </c>
       <c r="H121" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="L121"/>
     </row>
@@ -23325,7 +23331,7 @@
         <v>50</v>
       </c>
       <c r="D122" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="E122" t="n">
         <v>6</v>
@@ -23344,13 +23350,13 @@
         <v>60029</v>
       </c>
       <c r="B123" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="C123" t="n">
         <v>99</v>
       </c>
       <c r="D123" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="E123" t="n">
         <v>6</v>
@@ -23360,7 +23366,7 @@
         <v>3</v>
       </c>
       <c r="H123" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="L123"/>
     </row>
@@ -23369,13 +23375,13 @@
         <v>60030</v>
       </c>
       <c r="B124" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="C124" t="n">
         <v>60</v>
       </c>
       <c r="D124" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="E124" t="n">
         <v>6</v>
@@ -23385,7 +23391,7 @@
         <v>3</v>
       </c>
       <c r="H124" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="L124"/>
     </row>
@@ -23394,13 +23400,13 @@
         <v>60031</v>
       </c>
       <c r="B125" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="C125" t="n">
         <v>27</v>
       </c>
       <c r="D125" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="E125" t="n">
         <v>6</v>
@@ -23410,7 +23416,7 @@
         <v>3</v>
       </c>
       <c r="H125" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="L125"/>
     </row>
@@ -23425,7 +23431,7 @@
         <v>25</v>
       </c>
       <c r="D126" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="E126" t="n">
         <v>6</v>
@@ -23435,7 +23441,7 @@
         <v>3</v>
       </c>
       <c r="H126" t="s">
-        <v>110</v>
+        <v>738</v>
       </c>
       <c r="L126"/>
     </row>
@@ -23444,13 +23450,13 @@
         <v>60033</v>
       </c>
       <c r="B127" t="s">
-        <v>737</v>
+        <v>739</v>
       </c>
       <c r="C127" t="n">
         <v>25</v>
       </c>
       <c r="D127" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="E127" t="n">
         <v>6</v>
@@ -23460,7 +23466,7 @@
         <v>3</v>
       </c>
       <c r="H127" t="s">
-        <v>738</v>
+        <v>740</v>
       </c>
       <c r="L127"/>
     </row>
@@ -23469,13 +23475,13 @@
         <v>60034</v>
       </c>
       <c r="B128" t="s">
-        <v>739</v>
+        <v>741</v>
       </c>
       <c r="C128" t="n">
         <v>60</v>
       </c>
       <c r="D128" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="E128" t="n">
         <v>6</v>
@@ -23485,7 +23491,7 @@
         <v>3</v>
       </c>
       <c r="H128" t="s">
-        <v>740</v>
+        <v>742</v>
       </c>
       <c r="L128"/>
     </row>
@@ -23494,13 +23500,13 @@
         <v>60035</v>
       </c>
       <c r="B129" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="C129" t="n">
         <v>500</v>
       </c>
       <c r="D129" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="E129" t="n">
         <v>6</v>
@@ -23509,7 +23515,7 @@
         <v>3</v>
       </c>
       <c r="H129" t="s">
-        <v>741</v>
+        <v>743</v>
       </c>
       <c r="K129"/>
       <c r="L129"/>
@@ -23520,13 +23526,13 @@
         <v>60036</v>
       </c>
       <c r="B130" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="C130" t="n">
         <v>300</v>
       </c>
       <c r="D130" t="s">
-        <v>742</v>
+        <v>744</v>
       </c>
       <c r="E130" t="n">
         <v>6</v>
@@ -23535,7 +23541,7 @@
         <v>3</v>
       </c>
       <c r="H130" t="s">
-        <v>743</v>
+        <v>745</v>
       </c>
       <c r="K130"/>
       <c r="L130"/>
@@ -23546,13 +23552,13 @@
         <v>60037</v>
       </c>
       <c r="B131" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="C131" t="n">
         <v>50</v>
       </c>
       <c r="D131" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="E131" t="n">
         <v>6</v>
@@ -23561,7 +23567,7 @@
         <v>3</v>
       </c>
       <c r="H131" t="s">
-        <v>744</v>
+        <v>746</v>
       </c>
       <c r="K131"/>
       <c r="L131"/>
@@ -23572,13 +23578,13 @@
         <v>60038</v>
       </c>
       <c r="B132" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
       <c r="C132" t="n">
         <v>30</v>
       </c>
       <c r="D132" t="s">
-        <v>746</v>
+        <v>748</v>
       </c>
       <c r="E132" t="n">
         <v>6</v>
@@ -23587,7 +23593,7 @@
         <v>3</v>
       </c>
       <c r="H132" t="s">
-        <v>747</v>
+        <v>749</v>
       </c>
       <c r="K132"/>
       <c r="L132"/>
@@ -23598,13 +23604,13 @@
         <v>70001</v>
       </c>
       <c r="B133" t="s">
-        <v>748</v>
+        <v>750</v>
       </c>
       <c r="C133" t="n">
         <v>5</v>
       </c>
       <c r="D133" t="s">
-        <v>749</v>
+        <v>751</v>
       </c>
       <c r="E133" t="n">
         <v>7</v>
@@ -23612,7 +23618,7 @@
       <c r="F133"/>
       <c r="G133"/>
       <c r="H133" t="s">
-        <v>750</v>
+        <v>752</v>
       </c>
     </row>
     <row r="134">
@@ -23620,13 +23626,13 @@
         <v>70002</v>
       </c>
       <c r="B134" t="s">
-        <v>751</v>
+        <v>753</v>
       </c>
       <c r="C134" t="n">
         <v>5</v>
       </c>
       <c r="D134" t="s">
-        <v>749</v>
+        <v>751</v>
       </c>
       <c r="E134" t="n">
         <v>7</v>
@@ -23634,7 +23640,7 @@
       <c r="F134"/>
       <c r="G134"/>
       <c r="H134" t="s">
-        <v>752</v>
+        <v>754</v>
       </c>
     </row>
     <row r="135">
@@ -23642,13 +23648,13 @@
         <v>70003</v>
       </c>
       <c r="B135" t="s">
-        <v>753</v>
+        <v>755</v>
       </c>
       <c r="C135" t="n">
         <v>1</v>
       </c>
       <c r="D135" t="s">
-        <v>754</v>
+        <v>756</v>
       </c>
       <c r="E135" t="n">
         <v>7</v>
@@ -23656,7 +23662,7 @@
       <c r="F135"/>
       <c r="G135"/>
       <c r="H135" t="s">
-        <v>755</v>
+        <v>757</v>
       </c>
     </row>
     <row r="136">
@@ -23664,13 +23670,13 @@
         <v>70004</v>
       </c>
       <c r="B136" t="s">
-        <v>756</v>
+        <v>758</v>
       </c>
       <c r="C136" t="n">
         <v>7</v>
       </c>
       <c r="D136" t="s">
-        <v>754</v>
+        <v>756</v>
       </c>
       <c r="E136" t="n">
         <v>7</v>
@@ -23678,7 +23684,7 @@
       <c r="F136"/>
       <c r="G136"/>
       <c r="H136" t="s">
-        <v>757</v>
+        <v>759</v>
       </c>
     </row>
     <row r="137">
@@ -23686,13 +23692,13 @@
         <v>70005</v>
       </c>
       <c r="B137" t="s">
-        <v>758</v>
+        <v>760</v>
       </c>
       <c r="C137" t="n">
         <v>10</v>
       </c>
       <c r="D137" t="s">
-        <v>754</v>
+        <v>756</v>
       </c>
       <c r="E137" t="n">
         <v>7</v>
@@ -23700,7 +23706,7 @@
       <c r="F137"/>
       <c r="G137"/>
       <c r="H137" t="s">
-        <v>759</v>
+        <v>761</v>
       </c>
     </row>
     <row r="138">
@@ -23708,13 +23714,13 @@
         <v>70006</v>
       </c>
       <c r="B138" t="s">
-        <v>760</v>
+        <v>762</v>
       </c>
       <c r="C138" t="n">
         <v>7</v>
       </c>
       <c r="D138" t="s">
-        <v>754</v>
+        <v>756</v>
       </c>
       <c r="E138" t="n">
         <v>7</v>
@@ -23722,7 +23728,7 @@
       <c r="F138"/>
       <c r="G138"/>
       <c r="H138" t="s">
-        <v>761</v>
+        <v>763</v>
       </c>
     </row>
     <row r="139">
@@ -23730,13 +23736,13 @@
         <v>70007</v>
       </c>
       <c r="B139" t="s">
-        <v>762</v>
+        <v>764</v>
       </c>
       <c r="C139" t="n">
         <v>10</v>
       </c>
       <c r="D139" t="s">
-        <v>754</v>
+        <v>756</v>
       </c>
       <c r="E139" t="n">
         <v>7</v>
@@ -23744,7 +23750,7 @@
       <c r="F139"/>
       <c r="G139"/>
       <c r="H139" t="s">
-        <v>763</v>
+        <v>765</v>
       </c>
     </row>
     <row r="140">
@@ -23752,13 +23758,13 @@
         <v>70008</v>
       </c>
       <c r="B140" t="s">
-        <v>764</v>
+        <v>766</v>
       </c>
       <c r="C140" t="n">
         <v>1</v>
       </c>
       <c r="D140" t="s">
-        <v>765</v>
+        <v>767</v>
       </c>
       <c r="E140" t="n">
         <v>7</v>
@@ -23766,7 +23772,7 @@
       <c r="F140"/>
       <c r="G140"/>
       <c r="H140" t="s">
-        <v>766</v>
+        <v>768</v>
       </c>
     </row>
     <row r="141">
@@ -23774,13 +23780,13 @@
         <v>70009</v>
       </c>
       <c r="B141" t="s">
-        <v>767</v>
+        <v>769</v>
       </c>
       <c r="C141" t="n">
         <v>6</v>
       </c>
       <c r="D141" t="s">
-        <v>768</v>
+        <v>770</v>
       </c>
       <c r="E141" t="n">
         <v>7</v>
@@ -23788,7 +23794,7 @@
       <c r="F141"/>
       <c r="G141"/>
       <c r="H141" t="s">
-        <v>769</v>
+        <v>771</v>
       </c>
     </row>
     <row r="142">
@@ -23796,13 +23802,13 @@
         <v>70010</v>
       </c>
       <c r="B142" t="s">
-        <v>770</v>
+        <v>772</v>
       </c>
       <c r="C142" t="n">
         <v>1</v>
       </c>
       <c r="D142" t="s">
-        <v>771</v>
+        <v>773</v>
       </c>
       <c r="E142" t="n">
         <v>7</v>
@@ -23810,7 +23816,7 @@
       <c r="F142"/>
       <c r="G142"/>
       <c r="H142" t="s">
-        <v>772</v>
+        <v>774</v>
       </c>
     </row>
     <row r="143">
@@ -23818,13 +23824,13 @@
         <v>70011</v>
       </c>
       <c r="B143" t="s">
+        <v>775</v>
+      </c>
+      <c r="C143" t="n">
+        <v>1</v>
+      </c>
+      <c r="D143" t="s">
         <v>773</v>
-      </c>
-      <c r="C143" t="n">
-        <v>1</v>
-      </c>
-      <c r="D143" t="s">
-        <v>771</v>
       </c>
       <c r="E143" t="n">
         <v>7</v>
@@ -23832,7 +23838,7 @@
       <c r="F143"/>
       <c r="G143"/>
       <c r="H143" t="s">
-        <v>774</v>
+        <v>776</v>
       </c>
     </row>
     <row r="144">
@@ -23840,13 +23846,13 @@
         <v>70012</v>
       </c>
       <c r="B144" t="s">
-        <v>775</v>
+        <v>777</v>
       </c>
       <c r="C144" t="n">
         <v>1</v>
       </c>
       <c r="D144" t="s">
-        <v>771</v>
+        <v>773</v>
       </c>
       <c r="E144" t="n">
         <v>7</v>
@@ -23854,7 +23860,7 @@
       <c r="F144"/>
       <c r="G144"/>
       <c r="H144" t="s">
-        <v>776</v>
+        <v>778</v>
       </c>
     </row>
     <row r="145">
@@ -23862,19 +23868,19 @@
         <v>70013</v>
       </c>
       <c r="B145" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="C145" t="n">
         <v>5</v>
       </c>
       <c r="D145" t="s">
-        <v>777</v>
+        <v>779</v>
       </c>
       <c r="E145" t="n">
         <v>7</v>
       </c>
       <c r="H145" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
     </row>
     <row r="146">
@@ -23882,19 +23888,19 @@
         <v>70014</v>
       </c>
       <c r="B146" t="s">
-        <v>778</v>
+        <v>780</v>
       </c>
       <c r="C146" t="n">
         <v>1</v>
       </c>
       <c r="D146" t="s">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="E146" t="n">
         <v>7</v>
       </c>
       <c r="H146" t="s">
-        <v>780</v>
+        <v>782</v>
       </c>
     </row>
     <row r="147">
@@ -23908,13 +23914,13 @@
         <v>10</v>
       </c>
       <c r="D147" t="s">
-        <v>781</v>
+        <v>783</v>
       </c>
       <c r="E147" t="n">
         <v>7</v>
       </c>
       <c r="H147" t="s">
-        <v>782</v>
+        <v>784</v>
       </c>
     </row>
     <row r="148">
@@ -23922,19 +23928,19 @@
         <v>70016</v>
       </c>
       <c r="B148" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="C148" t="n">
         <v>20</v>
       </c>
       <c r="D148" t="s">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="E148" t="n">
         <v>7</v>
       </c>
       <c r="H148" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
     </row>
     <row r="149">
@@ -23942,19 +23948,19 @@
         <v>70017</v>
       </c>
       <c r="B149" t="s">
-        <v>783</v>
+        <v>785</v>
       </c>
       <c r="C149" t="n">
         <v>10</v>
       </c>
       <c r="D149" t="s">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="E149" t="n">
         <v>7</v>
       </c>
       <c r="H149" t="s">
-        <v>784</v>
+        <v>786</v>
       </c>
     </row>
     <row r="150">
@@ -23968,13 +23974,13 @@
         <v>20</v>
       </c>
       <c r="D150" t="s">
-        <v>785</v>
+        <v>787</v>
       </c>
       <c r="E150" t="n">
         <v>7</v>
       </c>
       <c r="H150" t="s">
-        <v>110</v>
+        <v>738</v>
       </c>
     </row>
     <row r="151">
@@ -23982,19 +23988,19 @@
         <v>70019</v>
       </c>
       <c r="B151" t="s">
-        <v>737</v>
+        <v>739</v>
       </c>
       <c r="C151" t="n">
         <v>10</v>
       </c>
       <c r="D151" t="s">
-        <v>785</v>
+        <v>787</v>
       </c>
       <c r="E151" t="n">
         <v>7</v>
       </c>
       <c r="H151" t="s">
-        <v>738</v>
+        <v>740</v>
       </c>
     </row>
     <row r="152">
@@ -24002,19 +24008,19 @@
         <v>70020</v>
       </c>
       <c r="B152" t="s">
-        <v>786</v>
+        <v>788</v>
       </c>
       <c r="C152" t="n">
         <v>20</v>
       </c>
       <c r="D152" t="s">
-        <v>785</v>
+        <v>787</v>
       </c>
       <c r="E152" t="n">
         <v>7</v>
       </c>
       <c r="H152" t="s">
-        <v>787</v>
+        <v>789</v>
       </c>
     </row>
     <row r="153">
@@ -24022,19 +24028,19 @@
         <v>70021</v>
       </c>
       <c r="B153" t="s">
-        <v>788</v>
+        <v>790</v>
       </c>
       <c r="C153" t="n">
         <v>20</v>
       </c>
       <c r="D153" t="s">
-        <v>789</v>
+        <v>791</v>
       </c>
       <c r="E153" t="n">
         <v>7</v>
       </c>
       <c r="H153" t="s">
-        <v>790</v>
+        <v>792</v>
       </c>
     </row>
     <row r="154">
@@ -24042,19 +24048,19 @@
         <v>70022</v>
       </c>
       <c r="B154" t="s">
-        <v>791</v>
+        <v>793</v>
       </c>
       <c r="C154" t="n">
         <v>10</v>
       </c>
       <c r="D154" t="s">
-        <v>789</v>
+        <v>791</v>
       </c>
       <c r="E154" t="n">
         <v>7</v>
       </c>
       <c r="H154" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
     </row>
     <row r="155">
@@ -24062,19 +24068,19 @@
         <v>70023</v>
       </c>
       <c r="B155" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="C155" t="n">
         <v>50</v>
       </c>
       <c r="D155" t="s">
-        <v>793</v>
+        <v>795</v>
       </c>
       <c r="E155" t="n">
         <v>7</v>
       </c>
       <c r="H155" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
     </row>
     <row r="156">
@@ -24082,19 +24088,19 @@
         <v>70024</v>
       </c>
       <c r="B156" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="C156" t="n">
         <v>50</v>
       </c>
       <c r="D156" t="s">
-        <v>793</v>
+        <v>795</v>
       </c>
       <c r="E156" t="n">
         <v>7</v>
       </c>
       <c r="H156" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
     </row>
   </sheetData>
@@ -24128,7 +24134,7 @@
         <v>5</v>
       </c>
       <c r="F1" t="s">
-        <v>794</v>
+        <v>796</v>
       </c>
       <c r="G1" t="s">
         <v>7</v>
@@ -24151,7 +24157,7 @@
         <v>100001</v>
       </c>
       <c r="B2" t="s">
-        <v>795</v>
+        <v>797</v>
       </c>
       <c r="C2" t="n">
         <v>8</v>
@@ -24178,7 +24184,7 @@
         <v>1</v>
       </c>
       <c r="K2" t="s">
-        <v>796</v>
+        <v>798</v>
       </c>
     </row>
   </sheetData>
@@ -24200,7 +24206,7 @@
         <v>130003</v>
       </c>
       <c r="B1" t="s">
-        <v>797</v>
+        <v>799</v>
       </c>
       <c r="C1"/>
       <c r="D1" t="n">
@@ -24224,7 +24230,7 @@
         <v>130005</v>
       </c>
       <c r="B2" t="s">
-        <v>798</v>
+        <v>800</v>
       </c>
       <c r="C2"/>
       <c r="D2" t="n">
@@ -24248,7 +24254,7 @@
         <v>130007</v>
       </c>
       <c r="B3" t="s">
-        <v>799</v>
+        <v>801</v>
       </c>
       <c r="C3"/>
       <c r="D3" t="n">
@@ -24272,7 +24278,7 @@
         <v>130009</v>
       </c>
       <c r="B4" t="s">
-        <v>800</v>
+        <v>802</v>
       </c>
       <c r="C4"/>
       <c r="D4" t="n">
@@ -24296,7 +24302,7 @@
         <v>130012</v>
       </c>
       <c r="B5" t="s">
-        <v>801</v>
+        <v>803</v>
       </c>
       <c r="C5"/>
       <c r="D5" t="n">
@@ -24334,25 +24340,25 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>802</v>
+        <v>804</v>
       </c>
       <c r="C1" t="s">
-        <v>803</v>
+        <v>805</v>
       </c>
       <c r="D1" t="s">
-        <v>804</v>
+        <v>806</v>
       </c>
       <c r="E1" t="s">
-        <v>805</v>
+        <v>807</v>
       </c>
       <c r="F1" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
       <c r="G1" t="s">
-        <v>807</v>
+        <v>809</v>
       </c>
       <c r="H1" t="s">
-        <v>794</v>
+        <v>796</v>
       </c>
     </row>
     <row r="2">
@@ -24360,22 +24366,22 @@
         <v>10001</v>
       </c>
       <c r="B2" t="s">
-        <v>808</v>
+        <v>810</v>
       </c>
       <c r="C2" t="s">
-        <v>809</v>
+        <v>811</v>
       </c>
       <c r="D2" t="s">
-        <v>810</v>
+        <v>812</v>
       </c>
       <c r="E2" t="n">
         <v>100093</v>
       </c>
       <c r="F2" t="s">
-        <v>811</v>
+        <v>813</v>
       </c>
       <c r="G2" t="s">
-        <v>812</v>
+        <v>814</v>
       </c>
       <c r="H2" t="n">
         <v>1</v>
@@ -24386,22 +24392,22 @@
         <v>20001</v>
       </c>
       <c r="B3" t="s">
-        <v>813</v>
+        <v>815</v>
       </c>
       <c r="C3" t="s">
-        <v>814</v>
+        <v>816</v>
       </c>
       <c r="D3" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="E3" t="n">
         <v>100094</v>
       </c>
       <c r="F3" t="s">
-        <v>811</v>
+        <v>813</v>
       </c>
       <c r="G3" t="s">
-        <v>812</v>
+        <v>814</v>
       </c>
       <c r="H3" t="n">
         <v>1</v>
@@ -24412,22 +24418,22 @@
         <v>30001</v>
       </c>
       <c r="B4" t="s">
-        <v>815</v>
+        <v>817</v>
       </c>
       <c r="C4" t="s">
-        <v>816</v>
+        <v>818</v>
       </c>
       <c r="D4" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="E4" t="n">
         <v>100095</v>
       </c>
       <c r="F4" t="s">
-        <v>811</v>
+        <v>813</v>
       </c>
       <c r="G4" t="s">
-        <v>812</v>
+        <v>814</v>
       </c>
       <c r="H4" t="n">
         <v>1</v>
